--- a/QSExt/Resource/TinySoftDBInfo.xlsx
+++ b/QSExt/Resource/TinySoftDBInfo.xlsx
@@ -1,24 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hst\Project\QSExt\QSExt\Resource\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="TableInfo" sheetId="2" r:id="rId1"/>
     <sheet name="FactorInfo" sheetId="1" r:id="rId2"/>
-    <sheet name="模版" sheetId="3" r:id="rId3"/>
+    <sheet name="ExchangeInfo" sheetId="4" r:id="rId3"/>
+    <sheet name="模版" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TableInfo!$A$1:$G$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FactorInfo!$A$1:$H$2679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TableInfo!$A$1:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FactorInfo!$A$1:$H$2704</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15877" uniqueCount="4607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15928" uniqueCount="4658">
   <si>
     <t>TableName</t>
   </si>
@@ -13859,6 +13855,159 @@
   </si>
   <si>
     <t>['单个账户当日净赎回份额上限']</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>Exchange</t>
+  </si>
+  <si>
+    <t>ExchangeName</t>
+  </si>
+  <si>
+    <t>.SH</t>
+  </si>
+  <si>
+    <t>SSE</t>
+  </si>
+  <si>
+    <t>上海证券交易所</t>
+  </si>
+  <si>
+    <t>.SZ</t>
+  </si>
+  <si>
+    <t>SZSE</t>
+  </si>
+  <si>
+    <t>深圳证券交易所</t>
+  </si>
+  <si>
+    <t>.BJ</t>
+  </si>
+  <si>
+    <t>BSE</t>
+  </si>
+  <si>
+    <t>北京证券交易所</t>
+  </si>
+  <si>
+    <t>.SHF</t>
+  </si>
+  <si>
+    <t>SHFE</t>
+  </si>
+  <si>
+    <t>上海期货交易所</t>
+  </si>
+  <si>
+    <t>.INE</t>
+  </si>
+  <si>
+    <t>INE</t>
+  </si>
+  <si>
+    <t>上海国际能源交易中心</t>
+  </si>
+  <si>
+    <t>.DCE</t>
+  </si>
+  <si>
+    <t>DCE</t>
+  </si>
+  <si>
+    <t>大连商品交易所</t>
+  </si>
+  <si>
+    <t>.CZC</t>
+  </si>
+  <si>
+    <t>CZCE</t>
+  </si>
+  <si>
+    <t>郑州商品交易所</t>
+  </si>
+  <si>
+    <t>.GFE</t>
+  </si>
+  <si>
+    <t>GFEX</t>
+  </si>
+  <si>
+    <t>广州期货交易所</t>
+  </si>
+  <si>
+    <t>.SGE</t>
+  </si>
+  <si>
+    <t>SGE</t>
+  </si>
+  <si>
+    <t>上海黄金交易所</t>
+  </si>
+  <si>
+    <t>.CFE</t>
+  </si>
+  <si>
+    <t>CFFEX</t>
+  </si>
+  <si>
+    <t>中国金融期货交易所</t>
+  </si>
+  <si>
+    <t>.IB</t>
+  </si>
+  <si>
+    <t>IB</t>
+  </si>
+  <si>
+    <t>银行间债券市场</t>
+  </si>
+  <si>
+    <t>.HK</t>
+  </si>
+  <si>
+    <t>HKEX</t>
+  </si>
+  <si>
+    <t>香港联交所</t>
+  </si>
+  <si>
+    <t>.O</t>
+  </si>
+  <si>
+    <t>NASDAQ</t>
+  </si>
+  <si>
+    <t>纳斯达克证券交易所</t>
+  </si>
+  <si>
+    <t>.N</t>
+  </si>
+  <si>
+    <t>NYSE</t>
+  </si>
+  <si>
+    <t>纽约证券交易所</t>
+  </si>
+  <si>
+    <t>.A</t>
+  </si>
+  <si>
+    <t>AMEX</t>
+  </si>
+  <si>
+    <t>美国证券交易所</t>
+  </si>
+  <si>
+    <t>.NQ</t>
+  </si>
+  <si>
+    <t>NEEQ</t>
+  </si>
+  <si>
+    <t>全国中小企业股份转让系统</t>
   </si>
 </sst>
 </file>
@@ -14474,10 +14623,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -14861,7 +15011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -15058,7 +15208,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -15078,7 +15228,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -15098,7 +15248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -15118,7 +15268,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -15138,7 +15288,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -16490,7 +16640,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G81" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G83" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16537,7 +16687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -16554,7 +16704,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -16571,7 +16721,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -16628,7 +16778,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -16645,7 +16795,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -16662,7 +16812,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -16679,7 +16829,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -17596,7 +17746,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -17613,7 +17763,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -17630,7 +17780,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -17667,7 +17817,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -17684,7 +17834,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -18621,7 +18771,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -18638,7 +18788,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -18658,7 +18808,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -18678,7 +18828,7 @@
         <v>10002</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -18698,7 +18848,7 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -19358,7 +19508,7 @@
         <v>10043</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -19378,7 +19528,7 @@
         <v>10044</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -19398,7 +19548,7 @@
         <v>10038</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -19418,7 +19568,7 @@
         <v>10039</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -19438,7 +19588,7 @@
         <v>10040</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -19458,7 +19608,7 @@
         <v>10041</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -19478,7 +19628,7 @@
         <v>10045</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -19498,7 +19648,7 @@
         <v>10046</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>23</v>
       </c>
@@ -19515,7 +19665,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>23</v>
       </c>
@@ -19632,7 +19782,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>23</v>
       </c>
@@ -19769,7 +19919,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>23</v>
       </c>
@@ -19786,7 +19936,7 @@
         <v>12018</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>23</v>
       </c>
@@ -19843,7 +19993,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>23</v>
       </c>
@@ -19860,7 +20010,7 @@
         <v>12023</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -19877,7 +20027,7 @@
         <v>12024</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>23</v>
       </c>
@@ -19894,7 +20044,7 @@
         <v>12025</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>23</v>
       </c>
@@ -19911,7 +20061,7 @@
         <v>12026</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>23</v>
       </c>
@@ -19928,7 +20078,7 @@
         <v>12027</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>23</v>
       </c>
@@ -19945,7 +20095,7 @@
         <v>12001</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>23</v>
       </c>
@@ -19962,7 +20112,7 @@
         <v>12002</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>23</v>
       </c>
@@ -19979,7 +20129,7 @@
         <v>12028</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -19996,7 +20146,7 @@
         <v>12029</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:7">
       <c r="A179" t="s">
         <v>23</v>
       </c>
@@ -20013,7 +20163,7 @@
         <v>12033</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:7">
       <c r="A180" t="s">
         <v>23</v>
       </c>
@@ -20030,7 +20180,7 @@
         <v>12034</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:7">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -20047,7 +20197,7 @@
         <v>12035</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:7">
       <c r="A182" t="s">
         <v>23</v>
       </c>
@@ -20064,7 +20214,7 @@
         <v>12036</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:7">
       <c r="A183" t="s">
         <v>23</v>
       </c>
@@ -20081,7 +20231,7 @@
         <v>12037</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:7">
       <c r="A184" t="s">
         <v>23</v>
       </c>
@@ -20318,7 +20468,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:7">
       <c r="A196" t="s">
         <v>23</v>
       </c>
@@ -20335,7 +20485,7 @@
         <v>12015</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:7">
       <c r="A197" t="s">
         <v>23</v>
       </c>
@@ -20352,7 +20502,7 @@
         <v>12048</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:7">
       <c r="A198" t="s">
         <v>23</v>
       </c>
@@ -20369,7 +20519,7 @@
         <v>12049</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:7">
       <c r="A199" t="s">
         <v>23</v>
       </c>
@@ -20386,7 +20536,7 @@
         <v>12050</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:7">
       <c r="A200" t="s">
         <v>23</v>
       </c>
@@ -20403,7 +20553,7 @@
         <v>12051</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:7">
       <c r="A201" t="s">
         <v>23</v>
       </c>
@@ -20420,7 +20570,7 @@
         <v>12052</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:7">
       <c r="A202" t="s">
         <v>23</v>
       </c>
@@ -20437,7 +20587,7 @@
         <v>12053</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:7">
       <c r="A203" t="s">
         <v>23</v>
       </c>
@@ -20754,7 +20904,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:7">
       <c r="A219" t="s">
         <v>23</v>
       </c>
@@ -20771,7 +20921,7 @@
         <v>12070</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
         <v>25</v>
       </c>
@@ -20788,7 +20938,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:7">
       <c r="A221" t="s">
         <v>25</v>
       </c>
@@ -20811,7 +20961,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
         <v>25</v>
       </c>
@@ -20831,7 +20981,7 @@
         <v>14001</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:7">
       <c r="A223" t="s">
         <v>25</v>
       </c>
@@ -20851,7 +21001,7 @@
         <v>14002</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
         <v>25</v>
       </c>
@@ -20871,7 +21021,7 @@
         <v>14003</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
         <v>29</v>
       </c>
@@ -20888,7 +21038,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:7">
       <c r="A226" t="s">
         <v>29</v>
       </c>
@@ -20908,7 +21058,7 @@
         <v>15001</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:7">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -20931,7 +21081,7 @@
         <v>15003</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:7">
       <c r="A228" t="s">
         <v>29</v>
       </c>
@@ -20951,7 +21101,7 @@
         <v>15004</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:7">
       <c r="A229" t="s">
         <v>29</v>
       </c>
@@ -20971,7 +21121,7 @@
         <v>15005</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
         <v>31</v>
       </c>
@@ -20988,7 +21138,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:7">
       <c r="A231" t="s">
         <v>31</v>
       </c>
@@ -21011,7 +21161,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:7">
       <c r="A232" t="s">
         <v>31</v>
       </c>
@@ -21307,7 +21457,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:7">
       <c r="A245" t="s">
         <v>31</v>
       </c>
@@ -21557,7 +21707,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:7">
       <c r="A256" t="s">
         <v>31</v>
       </c>
@@ -21577,7 +21727,7 @@
         <v>16042</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
         <v>33</v>
       </c>
@@ -21594,7 +21744,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>33</v>
       </c>
@@ -21617,7 +21767,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>33</v>
       </c>
@@ -21637,7 +21787,7 @@
         <v>17001</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>33</v>
       </c>
@@ -21703,7 +21853,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
         <v>35</v>
       </c>
@@ -21720,7 +21870,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>35</v>
       </c>
@@ -21740,7 +21890,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>35</v>
       </c>
@@ -21760,7 +21910,7 @@
         <v>18001</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>35</v>
       </c>
@@ -21780,7 +21930,7 @@
         <v>18002</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>35</v>
       </c>
@@ -21800,7 +21950,7 @@
         <v>18003</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>35</v>
       </c>
@@ -21820,7 +21970,7 @@
         <v>18004</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>35</v>
       </c>
@@ -21840,7 +21990,7 @@
         <v>18005</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>35</v>
       </c>
@@ -22001,7 +22151,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>35</v>
       </c>
@@ -22021,7 +22171,7 @@
         <v>18012</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>35</v>
       </c>
@@ -22041,7 +22191,7 @@
         <v>18013</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>35</v>
       </c>
@@ -22061,7 +22211,7 @@
         <v>18015</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>35</v>
       </c>
@@ -22081,7 +22231,7 @@
         <v>18014</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:5">
       <c r="A281" t="s">
         <v>39</v>
       </c>
@@ -22098,7 +22248,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>39</v>
       </c>
@@ -22121,7 +22271,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>39</v>
       </c>
@@ -22141,7 +22291,7 @@
         <v>20001</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>39</v>
       </c>
@@ -22184,7 +22334,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>39</v>
       </c>
@@ -22204,7 +22354,7 @@
         <v>20008</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>39</v>
       </c>
@@ -22270,7 +22420,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>39</v>
       </c>
@@ -22382,7 +22532,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>39</v>
       </c>
@@ -22402,7 +22552,7 @@
         <v>20030</v>
       </c>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>39</v>
       </c>
@@ -22422,7 +22572,7 @@
         <v>20031</v>
       </c>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:7">
       <c r="A297" t="s">
         <v>39</v>
       </c>
@@ -22442,7 +22592,7 @@
         <v>20032</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:7">
       <c r="A298" t="s">
         <v>39</v>
       </c>
@@ -22462,7 +22612,7 @@
         <v>20033</v>
       </c>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:7">
       <c r="A299" t="s">
         <v>39</v>
       </c>
@@ -22482,7 +22632,7 @@
         <v>20034</v>
       </c>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:7">
       <c r="A300" t="s">
         <v>39</v>
       </c>
@@ -22502,7 +22652,7 @@
         <v>20036</v>
       </c>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:7">
       <c r="A301" t="s">
         <v>39</v>
       </c>
@@ -22568,7 +22718,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:7">
       <c r="A304" t="s">
         <v>39</v>
       </c>
@@ -22588,7 +22738,7 @@
         <v>20043</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:7">
       <c r="A305" t="s">
         <v>39</v>
       </c>
@@ -22608,7 +22758,7 @@
         <v>20044</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:7">
       <c r="A306" t="s">
         <v>39</v>
       </c>
@@ -22628,7 +22778,7 @@
         <v>20069</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:5">
       <c r="A307" t="s">
         <v>40</v>
       </c>
@@ -22645,7 +22795,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:7">
       <c r="A308" t="s">
         <v>40</v>
       </c>
@@ -22668,7 +22818,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:7">
       <c r="A309" t="s">
         <v>40</v>
       </c>
@@ -22688,7 +22838,7 @@
         <v>22001</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:7">
       <c r="A310" t="s">
         <v>40</v>
       </c>
@@ -22708,7 +22858,7 @@
         <v>22002</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:7">
       <c r="A311" t="s">
         <v>40</v>
       </c>
@@ -22728,7 +22878,7 @@
         <v>22003</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:7">
       <c r="A312" t="s">
         <v>40</v>
       </c>
@@ -22771,7 +22921,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:7">
       <c r="A314" t="s">
         <v>40</v>
       </c>
@@ -22791,7 +22941,7 @@
         <v>22006</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:7">
       <c r="A315" t="s">
         <v>40</v>
       </c>
@@ -22811,7 +22961,7 @@
         <v>22007</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:7">
       <c r="A316" t="s">
         <v>40</v>
       </c>
@@ -22831,7 +22981,7 @@
         <v>22008</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:7">
       <c r="A317" t="s">
         <v>40</v>
       </c>
@@ -22851,7 +23001,7 @@
         <v>22009</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:7">
       <c r="A318" t="s">
         <v>40</v>
       </c>
@@ -22894,7 +23044,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:7">
       <c r="A320" t="s">
         <v>40</v>
       </c>
@@ -23234,7 +23384,7 @@
         <v>22028</v>
       </c>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:7">
       <c r="A337" t="s">
         <v>40</v>
       </c>
@@ -23254,7 +23404,7 @@
         <v>22029</v>
       </c>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:7">
       <c r="A338" t="s">
         <v>40</v>
       </c>
@@ -23274,7 +23424,7 @@
         <v>22030</v>
       </c>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:7">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -23294,7 +23444,7 @@
         <v>22031</v>
       </c>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:7">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -23452,7 +23602,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:7">
       <c r="A347" t="s">
         <v>40</v>
       </c>
@@ -23472,7 +23622,7 @@
         <v>22039</v>
       </c>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:7">
       <c r="A348" t="s">
         <v>40</v>
       </c>
@@ -23975,7 +24125,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:7">
       <c r="A370" t="s">
         <v>40</v>
       </c>
@@ -24087,7 +24237,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:5">
       <c r="A375" t="s">
         <v>41</v>
       </c>
@@ -24104,7 +24254,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:7">
       <c r="A376" t="s">
         <v>41</v>
       </c>
@@ -24150,7 +24300,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" spans="1:7">
       <c r="A378" t="s">
         <v>41</v>
       </c>
@@ -24170,7 +24320,7 @@
         <v>24002</v>
       </c>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:7">
       <c r="A379" t="s">
         <v>41</v>
       </c>
@@ -24236,7 +24386,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:7">
       <c r="A382" t="s">
         <v>41</v>
       </c>
@@ -24256,7 +24406,7 @@
         <v>24006</v>
       </c>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:7">
       <c r="A383" t="s">
         <v>41</v>
       </c>
@@ -24276,7 +24426,7 @@
         <v>24007</v>
       </c>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:7">
       <c r="A384" t="s">
         <v>41</v>
       </c>
@@ -24296,7 +24446,7 @@
         <v>24008</v>
       </c>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" spans="1:7">
       <c r="A385" t="s">
         <v>41</v>
       </c>
@@ -24316,7 +24466,7 @@
         <v>24009</v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" spans="1:7">
       <c r="A386" t="s">
         <v>41</v>
       </c>
@@ -24428,7 +24578,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" spans="1:7">
       <c r="A391" t="s">
         <v>41</v>
       </c>
@@ -24448,7 +24598,7 @@
         <v>24015</v>
       </c>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" spans="1:5">
       <c r="A392" t="s">
         <v>42</v>
       </c>
@@ -24465,7 +24615,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" spans="1:7">
       <c r="A393" t="s">
         <v>42</v>
       </c>
@@ -24511,7 +24661,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:7">
       <c r="A395" t="s">
         <v>42</v>
       </c>
@@ -24531,7 +24681,7 @@
         <v>26002</v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:7">
       <c r="A396" t="s">
         <v>42</v>
       </c>
@@ -24597,7 +24747,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" spans="1:7">
       <c r="A399" t="s">
         <v>42</v>
       </c>
@@ -24617,7 +24767,7 @@
         <v>26006</v>
       </c>
     </row>
-    <row r="400" spans="1:8">
+    <row r="400" spans="1:7">
       <c r="A400" t="s">
         <v>42</v>
       </c>
@@ -24637,7 +24787,7 @@
         <v>26007</v>
       </c>
     </row>
-    <row r="401" spans="1:8">
+    <row r="401" spans="1:7">
       <c r="A401" t="s">
         <v>42</v>
       </c>
@@ -24657,7 +24807,7 @@
         <v>26008</v>
       </c>
     </row>
-    <row r="402" spans="1:8">
+    <row r="402" spans="1:7">
       <c r="A402" t="s">
         <v>42</v>
       </c>
@@ -24677,7 +24827,7 @@
         <v>26009</v>
       </c>
     </row>
-    <row r="403" spans="1:8">
+    <row r="403" spans="1:7">
       <c r="A403" t="s">
         <v>42</v>
       </c>
@@ -24789,7 +24939,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="408" spans="1:8">
+    <row r="408" spans="1:7">
       <c r="A408" t="s">
         <v>42</v>
       </c>
@@ -24809,7 +24959,7 @@
         <v>26015</v>
       </c>
     </row>
-    <row r="409" spans="1:8">
+    <row r="409" spans="1:5">
       <c r="A409" t="s">
         <v>43</v>
       </c>
@@ -24826,7 +24976,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="410" spans="1:8">
+    <row r="410" spans="1:7">
       <c r="A410" t="s">
         <v>43</v>
       </c>
@@ -24849,7 +24999,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="411" spans="1:8">
+    <row r="411" spans="1:7">
       <c r="A411" t="s">
         <v>43</v>
       </c>
@@ -24869,7 +25019,7 @@
         <v>27001</v>
       </c>
     </row>
-    <row r="412" spans="1:8">
+    <row r="412" spans="1:7">
       <c r="A412" t="s">
         <v>43</v>
       </c>
@@ -24889,7 +25039,7 @@
         <v>27002</v>
       </c>
     </row>
-    <row r="413" spans="1:8">
+    <row r="413" spans="1:7">
       <c r="A413" t="s">
         <v>43</v>
       </c>
@@ -24909,7 +25059,7 @@
         <v>27003</v>
       </c>
     </row>
-    <row r="414" spans="1:8">
+    <row r="414" spans="1:7">
       <c r="A414" t="s">
         <v>43</v>
       </c>
@@ -24929,7 +25079,7 @@
         <v>27004</v>
       </c>
     </row>
-    <row r="415" spans="1:8">
+    <row r="415" spans="1:7">
       <c r="A415" t="s">
         <v>43</v>
       </c>
@@ -24949,7 +25099,7 @@
         <v>27005</v>
       </c>
     </row>
-    <row r="416" spans="1:8">
+    <row r="416" spans="1:7">
       <c r="A416" t="s">
         <v>43</v>
       </c>
@@ -26249,7 +26399,7 @@
         <v>27070</v>
       </c>
     </row>
-    <row r="481" spans="1:8">
+    <row r="481" spans="1:7">
       <c r="A481" t="s">
         <v>43</v>
       </c>
@@ -26269,7 +26419,7 @@
         <v>27071</v>
       </c>
     </row>
-    <row r="482" spans="1:8">
+    <row r="482" spans="1:7">
       <c r="A482" t="s">
         <v>43</v>
       </c>
@@ -26289,7 +26439,7 @@
         <v>27072</v>
       </c>
     </row>
-    <row r="483" spans="1:8">
+    <row r="483" spans="1:7">
       <c r="A483" t="s">
         <v>43</v>
       </c>
@@ -26309,7 +26459,7 @@
         <v>27073</v>
       </c>
     </row>
-    <row r="484" spans="1:8">
+    <row r="484" spans="1:7">
       <c r="A484" t="s">
         <v>43</v>
       </c>
@@ -26329,7 +26479,7 @@
         <v>27074</v>
       </c>
     </row>
-    <row r="485" spans="1:8">
+    <row r="485" spans="1:7">
       <c r="A485" t="s">
         <v>43</v>
       </c>
@@ -26349,7 +26499,7 @@
         <v>27075</v>
       </c>
     </row>
-    <row r="486" spans="1:8">
+    <row r="486" spans="1:7">
       <c r="A486" t="s">
         <v>43</v>
       </c>
@@ -26369,7 +26519,7 @@
         <v>27076</v>
       </c>
     </row>
-    <row r="487" spans="1:8">
+    <row r="487" spans="1:7">
       <c r="A487" t="s">
         <v>43</v>
       </c>
@@ -26389,7 +26539,7 @@
         <v>27077</v>
       </c>
     </row>
-    <row r="488" spans="1:8">
+    <row r="488" spans="1:7">
       <c r="A488" t="s">
         <v>43</v>
       </c>
@@ -26409,7 +26559,7 @@
         <v>27078</v>
       </c>
     </row>
-    <row r="489" spans="1:8">
+    <row r="489" spans="1:7">
       <c r="A489" t="s">
         <v>43</v>
       </c>
@@ -26429,7 +26579,7 @@
         <v>27079</v>
       </c>
     </row>
-    <row r="490" spans="1:8">
+    <row r="490" spans="1:7">
       <c r="A490" t="s">
         <v>43</v>
       </c>
@@ -26449,7 +26599,7 @@
         <v>27080</v>
       </c>
     </row>
-    <row r="491" spans="1:8">
+    <row r="491" spans="1:5">
       <c r="A491" t="s">
         <v>44</v>
       </c>
@@ -26466,7 +26616,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="492" spans="1:8">
+    <row r="492" spans="1:7">
       <c r="A492" t="s">
         <v>44</v>
       </c>
@@ -26489,7 +26639,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="493" spans="1:8">
+    <row r="493" spans="1:7">
       <c r="A493" t="s">
         <v>44</v>
       </c>
@@ -26532,7 +26682,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="495" spans="1:8">
+    <row r="495" spans="1:7">
       <c r="A495" t="s">
         <v>44</v>
       </c>
@@ -26552,7 +26702,7 @@
         <v>28003</v>
       </c>
     </row>
-    <row r="496" spans="1:8">
+    <row r="496" spans="1:5">
       <c r="A496" t="s">
         <v>45</v>
       </c>
@@ -26569,7 +26719,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="497" spans="1:8">
+    <row r="497" spans="1:7">
       <c r="A497" t="s">
         <v>45</v>
       </c>
@@ -26592,7 +26742,7 @@
         <v>29001</v>
       </c>
     </row>
-    <row r="498" spans="1:8">
+    <row r="498" spans="1:7">
       <c r="A498" t="s">
         <v>45</v>
       </c>
@@ -26612,7 +26762,7 @@
         <v>29002</v>
       </c>
     </row>
-    <row r="499" spans="1:8">
+    <row r="499" spans="1:7">
       <c r="A499" t="s">
         <v>45</v>
       </c>
@@ -26632,7 +26782,7 @@
         <v>29003</v>
       </c>
     </row>
-    <row r="500" spans="1:8">
+    <row r="500" spans="1:7">
       <c r="A500" t="s">
         <v>45</v>
       </c>
@@ -26652,7 +26802,7 @@
         <v>29004</v>
       </c>
     </row>
-    <row r="501" spans="1:8">
+    <row r="501" spans="1:7">
       <c r="A501" t="s">
         <v>45</v>
       </c>
@@ -26695,7 +26845,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="503" spans="1:8">
+    <row r="503" spans="1:5">
       <c r="A503" t="s">
         <v>46</v>
       </c>
@@ -26712,7 +26862,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="504" spans="1:8">
+    <row r="504" spans="1:7">
       <c r="A504" t="s">
         <v>46</v>
       </c>
@@ -26735,7 +26885,7 @@
         <v>30001</v>
       </c>
     </row>
-    <row r="505" spans="1:8">
+    <row r="505" spans="1:7">
       <c r="A505" t="s">
         <v>46</v>
       </c>
@@ -26758,7 +26908,7 @@
         <v>30002</v>
       </c>
     </row>
-    <row r="506" spans="1:8">
+    <row r="506" spans="1:7">
       <c r="A506" t="s">
         <v>46</v>
       </c>
@@ -26778,7 +26928,7 @@
         <v>30003</v>
       </c>
     </row>
-    <row r="507" spans="1:8">
+    <row r="507" spans="1:7">
       <c r="A507" t="s">
         <v>46</v>
       </c>
@@ -26798,7 +26948,7 @@
         <v>30004</v>
       </c>
     </row>
-    <row r="508" spans="1:8">
+    <row r="508" spans="1:7">
       <c r="A508" t="s">
         <v>46</v>
       </c>
@@ -26818,7 +26968,7 @@
         <v>30005</v>
       </c>
     </row>
-    <row r="509" spans="1:8">
+    <row r="509" spans="1:7">
       <c r="A509" t="s">
         <v>46</v>
       </c>
@@ -26838,7 +26988,7 @@
         <v>30006</v>
       </c>
     </row>
-    <row r="510" spans="1:8">
+    <row r="510" spans="1:7">
       <c r="A510" t="s">
         <v>46</v>
       </c>
@@ -26858,7 +27008,7 @@
         <v>30007</v>
       </c>
     </row>
-    <row r="511" spans="1:8">
+    <row r="511" spans="1:7">
       <c r="A511" t="s">
         <v>46</v>
       </c>
@@ -26878,7 +27028,7 @@
         <v>30008</v>
       </c>
     </row>
-    <row r="512" spans="1:8">
+    <row r="512" spans="1:7">
       <c r="A512" t="s">
         <v>46</v>
       </c>
@@ -27059,7 +27209,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="520" spans="1:8">
+    <row r="520" spans="1:7">
       <c r="A520" t="s">
         <v>46</v>
       </c>
@@ -27079,7 +27229,7 @@
         <v>30017</v>
       </c>
     </row>
-    <row r="521" spans="1:8">
+    <row r="521" spans="1:7">
       <c r="A521" t="s">
         <v>46</v>
       </c>
@@ -27099,7 +27249,7 @@
         <v>30018</v>
       </c>
     </row>
-    <row r="522" spans="1:8">
+    <row r="522" spans="1:5">
       <c r="A522" t="s">
         <v>48</v>
       </c>
@@ -27116,7 +27266,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="523" spans="1:8">
+    <row r="523" spans="1:7">
       <c r="A523" t="s">
         <v>48</v>
       </c>
@@ -27136,7 +27286,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="524" spans="1:8">
+    <row r="524" spans="1:7">
       <c r="A524" t="s">
         <v>48</v>
       </c>
@@ -27159,7 +27309,7 @@
         <v>40001</v>
       </c>
     </row>
-    <row r="525" spans="1:8">
+    <row r="525" spans="1:7">
       <c r="A525" t="s">
         <v>48</v>
       </c>
@@ -27179,7 +27329,7 @@
         <v>40002</v>
       </c>
     </row>
-    <row r="526" spans="1:8">
+    <row r="526" spans="1:7">
       <c r="A526" t="s">
         <v>48</v>
       </c>
@@ -27245,7 +27395,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="529" spans="1:8">
+    <row r="529" spans="1:7">
       <c r="A529" t="s">
         <v>48</v>
       </c>
@@ -27265,7 +27415,7 @@
         <v>40007</v>
       </c>
     </row>
-    <row r="530" spans="1:8">
+    <row r="530" spans="1:7">
       <c r="A530" t="s">
         <v>48</v>
       </c>
@@ -27285,7 +27435,7 @@
         <v>40008</v>
       </c>
     </row>
-    <row r="531" spans="1:8">
+    <row r="531" spans="1:7">
       <c r="A531" t="s">
         <v>48</v>
       </c>
@@ -27305,7 +27455,7 @@
         <v>40009</v>
       </c>
     </row>
-    <row r="532" spans="1:8">
+    <row r="532" spans="1:7">
       <c r="A532" t="s">
         <v>48</v>
       </c>
@@ -27325,7 +27475,7 @@
         <v>40011</v>
       </c>
     </row>
-    <row r="533" spans="1:8">
+    <row r="533" spans="1:7">
       <c r="A533" t="s">
         <v>48</v>
       </c>
@@ -27345,7 +27495,7 @@
         <v>40010</v>
       </c>
     </row>
-    <row r="534" spans="1:8">
+    <row r="534" spans="1:7">
       <c r="A534" t="s">
         <v>48</v>
       </c>
@@ -27365,7 +27515,7 @@
         <v>40004</v>
       </c>
     </row>
-    <row r="535" spans="1:8">
+    <row r="535" spans="1:5">
       <c r="A535" t="s">
         <v>49</v>
       </c>
@@ -27382,7 +27532,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="536" spans="1:8">
+    <row r="536" spans="1:7">
       <c r="A536" t="s">
         <v>49</v>
       </c>
@@ -27402,7 +27552,7 @@
         <v>41001</v>
       </c>
     </row>
-    <row r="537" spans="1:8">
+    <row r="537" spans="1:7">
       <c r="A537" t="s">
         <v>49</v>
       </c>
@@ -27655,7 +27805,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="548" spans="1:8">
+    <row r="548" spans="1:5">
       <c r="A548" t="s">
         <v>50</v>
       </c>
@@ -27672,7 +27822,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="549" spans="1:8">
+    <row r="549" spans="1:7">
       <c r="A549" t="s">
         <v>50</v>
       </c>
@@ -27695,7 +27845,7 @@
         <v>122001</v>
       </c>
     </row>
-    <row r="550" spans="1:8">
+    <row r="550" spans="1:7">
       <c r="A550" t="s">
         <v>50</v>
       </c>
@@ -27715,7 +27865,7 @@
         <v>122002</v>
       </c>
     </row>
-    <row r="551" spans="1:8">
+    <row r="551" spans="1:7">
       <c r="A551" t="s">
         <v>50</v>
       </c>
@@ -27735,7 +27885,7 @@
         <v>122003</v>
       </c>
     </row>
-    <row r="552" spans="1:8">
+    <row r="552" spans="1:7">
       <c r="A552" t="s">
         <v>50</v>
       </c>
@@ -27755,7 +27905,7 @@
         <v>122004</v>
       </c>
     </row>
-    <row r="553" spans="1:8">
+    <row r="553" spans="1:5">
       <c r="A553" t="s">
         <v>51</v>
       </c>
@@ -27772,7 +27922,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="554" spans="1:8">
+    <row r="554" spans="1:7">
       <c r="A554" t="s">
         <v>51</v>
       </c>
@@ -27864,7 +28014,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="558" spans="1:8">
+    <row r="558" spans="1:7">
       <c r="A558" t="s">
         <v>51</v>
       </c>
@@ -27884,7 +28034,7 @@
         <v>124005</v>
       </c>
     </row>
-    <row r="559" spans="1:8">
+    <row r="559" spans="1:7">
       <c r="A559" t="s">
         <v>51</v>
       </c>
@@ -27904,7 +28054,7 @@
         <v>124006</v>
       </c>
     </row>
-    <row r="560" spans="1:8">
+    <row r="560" spans="1:7">
       <c r="A560" t="s">
         <v>51</v>
       </c>
@@ -27924,7 +28074,7 @@
         <v>124007</v>
       </c>
     </row>
-    <row r="561" spans="1:8">
+    <row r="561" spans="1:7">
       <c r="A561" t="s">
         <v>51</v>
       </c>
@@ -27944,7 +28094,7 @@
         <v>124008</v>
       </c>
     </row>
-    <row r="562" spans="1:8">
+    <row r="562" spans="1:7">
       <c r="A562" t="s">
         <v>51</v>
       </c>
@@ -27964,7 +28114,7 @@
         <v>124009</v>
       </c>
     </row>
-    <row r="563" spans="1:8">
+    <row r="563" spans="1:5">
       <c r="A563" t="s">
         <v>52</v>
       </c>
@@ -27981,7 +28131,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="564" spans="1:8">
+    <row r="564" spans="1:7">
       <c r="A564" t="s">
         <v>52</v>
       </c>
@@ -28188,7 +28338,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="573" spans="1:8">
+    <row r="573" spans="1:5">
       <c r="A573" t="s">
         <v>53</v>
       </c>
@@ -28205,7 +28355,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="574" spans="1:8">
+    <row r="574" spans="1:7">
       <c r="A574" t="s">
         <v>53</v>
       </c>
@@ -28228,7 +28378,7 @@
         <v>127001</v>
       </c>
     </row>
-    <row r="575" spans="1:8">
+    <row r="575" spans="1:7">
       <c r="A575" t="s">
         <v>53</v>
       </c>
@@ -28248,7 +28398,7 @@
         <v>127002</v>
       </c>
     </row>
-    <row r="576" spans="1:8">
+    <row r="576" spans="1:7">
       <c r="A576" t="s">
         <v>53</v>
       </c>
@@ -28331,7 +28481,7 @@
         <v>127006</v>
       </c>
     </row>
-    <row r="580" spans="1:7">
+    <row r="580" spans="1:5">
       <c r="A580" t="s">
         <v>54</v>
       </c>
@@ -28571,7 +28721,7 @@
         <v>129011</v>
       </c>
     </row>
-    <row r="592" spans="1:7">
+    <row r="592" spans="1:5">
       <c r="A592" t="s">
         <v>55</v>
       </c>
@@ -28588,7 +28738,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="593" spans="1:8">
+    <row r="593" spans="1:7">
       <c r="A593" t="s">
         <v>55</v>
       </c>
@@ -28841,7 +28991,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="604" spans="1:8">
+    <row r="604" spans="1:5">
       <c r="A604" t="s">
         <v>57</v>
       </c>
@@ -28858,7 +29008,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="605" spans="1:8">
+    <row r="605" spans="1:7">
       <c r="A605" t="s">
         <v>57</v>
       </c>
@@ -28881,7 +29031,7 @@
         <v>131001</v>
       </c>
     </row>
-    <row r="606" spans="1:8">
+    <row r="606" spans="1:7">
       <c r="A606" t="s">
         <v>57</v>
       </c>
@@ -28901,7 +29051,7 @@
         <v>131002</v>
       </c>
     </row>
-    <row r="607" spans="1:8">
+    <row r="607" spans="1:7">
       <c r="A607" t="s">
         <v>57</v>
       </c>
@@ -28990,7 +29140,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="611" spans="1:8">
+    <row r="611" spans="1:7">
       <c r="A611" t="s">
         <v>57</v>
       </c>
@@ -29013,7 +29163,7 @@
         <v>131007</v>
       </c>
     </row>
-    <row r="612" spans="1:8">
+    <row r="612" spans="1:5">
       <c r="A612" t="s">
         <v>58</v>
       </c>
@@ -29030,7 +29180,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="613" spans="1:8">
+    <row r="613" spans="1:7">
       <c r="A613" t="s">
         <v>58</v>
       </c>
@@ -29053,7 +29203,7 @@
         <v>132001</v>
       </c>
     </row>
-    <row r="614" spans="1:8">
+    <row r="614" spans="1:7">
       <c r="A614" t="s">
         <v>58</v>
       </c>
@@ -29096,7 +29246,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="616" spans="1:8">
+    <row r="616" spans="1:5">
       <c r="A616" t="s">
         <v>64</v>
       </c>
@@ -29113,7 +29263,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="617" spans="1:8">
+    <row r="617" spans="1:7">
       <c r="A617" t="s">
         <v>64</v>
       </c>
@@ -29133,7 +29283,7 @@
         <v>302000</v>
       </c>
     </row>
-    <row r="618" spans="1:8">
+    <row r="618" spans="1:7">
       <c r="A618" t="s">
         <v>64</v>
       </c>
@@ -29153,7 +29303,7 @@
         <v>302001</v>
       </c>
     </row>
-    <row r="619" spans="1:8">
+    <row r="619" spans="1:7">
       <c r="A619" t="s">
         <v>64</v>
       </c>
@@ -29173,7 +29323,7 @@
         <v>302002</v>
       </c>
     </row>
-    <row r="620" spans="1:8">
+    <row r="620" spans="1:7">
       <c r="A620" t="s">
         <v>64</v>
       </c>
@@ -29193,7 +29343,7 @@
         <v>302003</v>
       </c>
     </row>
-    <row r="621" spans="1:8">
+    <row r="621" spans="1:7">
       <c r="A621" t="s">
         <v>64</v>
       </c>
@@ -29305,7 +29455,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="626" spans="1:8">
+    <row r="626" spans="1:7">
       <c r="A626" t="s">
         <v>64</v>
       </c>
@@ -29325,7 +29475,7 @@
         <v>302009</v>
       </c>
     </row>
-    <row r="627" spans="1:8">
+    <row r="627" spans="1:7">
       <c r="A627" t="s">
         <v>64</v>
       </c>
@@ -29391,7 +29541,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="630" spans="1:8">
+    <row r="630" spans="1:7">
       <c r="A630" t="s">
         <v>64</v>
       </c>
@@ -29411,7 +29561,7 @@
         <v>302013</v>
       </c>
     </row>
-    <row r="631" spans="1:8">
+    <row r="631" spans="1:7">
       <c r="A631" t="s">
         <v>64</v>
       </c>
@@ -29431,7 +29581,7 @@
         <v>302014</v>
       </c>
     </row>
-    <row r="632" spans="1:8">
+    <row r="632" spans="1:7">
       <c r="A632" t="s">
         <v>64</v>
       </c>
@@ -29451,7 +29601,7 @@
         <v>302015</v>
       </c>
     </row>
-    <row r="633" spans="1:8">
+    <row r="633" spans="1:7">
       <c r="A633" t="s">
         <v>64</v>
       </c>
@@ -29471,7 +29621,7 @@
         <v>302016</v>
       </c>
     </row>
-    <row r="634" spans="1:8">
+    <row r="634" spans="1:7">
       <c r="A634" t="s">
         <v>64</v>
       </c>
@@ -29537,7 +29687,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="637" spans="1:8">
+    <row r="637" spans="1:7">
       <c r="A637" t="s">
         <v>64</v>
       </c>
@@ -29580,7 +29730,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="639" spans="1:8">
+    <row r="639" spans="1:7">
       <c r="A639" t="s">
         <v>64</v>
       </c>
@@ -29600,7 +29750,7 @@
         <v>302021</v>
       </c>
     </row>
-    <row r="640" spans="1:8">
+    <row r="640" spans="1:7">
       <c r="A640" t="s">
         <v>64</v>
       </c>
@@ -29940,7 +30090,7 @@
         <v>302038</v>
       </c>
     </row>
-    <row r="657" spans="1:8">
+    <row r="657" spans="1:7">
       <c r="A657" t="s">
         <v>64</v>
       </c>
@@ -29960,7 +30110,7 @@
         <v>302040</v>
       </c>
     </row>
-    <row r="658" spans="1:8">
+    <row r="658" spans="1:7">
       <c r="A658" t="s">
         <v>64</v>
       </c>
@@ -29980,7 +30130,7 @@
         <v>302042</v>
       </c>
     </row>
-    <row r="659" spans="1:8">
+    <row r="659" spans="1:7">
       <c r="A659" t="s">
         <v>64</v>
       </c>
@@ -30000,7 +30150,7 @@
         <v>302043</v>
       </c>
     </row>
-    <row r="660" spans="1:8">
+    <row r="660" spans="1:7">
       <c r="A660" t="s">
         <v>64</v>
       </c>
@@ -30020,7 +30170,7 @@
         <v>302044</v>
       </c>
     </row>
-    <row r="661" spans="1:8">
+    <row r="661" spans="1:7">
       <c r="A661" t="s">
         <v>64</v>
       </c>
@@ -30040,7 +30190,7 @@
         <v>302045</v>
       </c>
     </row>
-    <row r="662" spans="1:8">
+    <row r="662" spans="1:7">
       <c r="A662" t="s">
         <v>64</v>
       </c>
@@ -30060,7 +30210,7 @@
         <v>302046</v>
       </c>
     </row>
-    <row r="663" spans="1:8">
+    <row r="663" spans="1:7">
       <c r="A663" t="s">
         <v>64</v>
       </c>
@@ -30080,7 +30230,7 @@
         <v>302047</v>
       </c>
     </row>
-    <row r="664" spans="1:8">
+    <row r="664" spans="1:5">
       <c r="A664" t="s">
         <v>66</v>
       </c>
@@ -30097,7 +30247,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="665" spans="1:8">
+    <row r="665" spans="1:7">
       <c r="A665" t="s">
         <v>66</v>
       </c>
@@ -30117,7 +30267,7 @@
         <v>303010</v>
       </c>
     </row>
-    <row r="666" spans="1:8">
+    <row r="666" spans="1:7">
       <c r="A666" t="s">
         <v>66</v>
       </c>
@@ -30137,7 +30287,7 @@
         <v>303001</v>
       </c>
     </row>
-    <row r="667" spans="1:8">
+    <row r="667" spans="1:7">
       <c r="A667" t="s">
         <v>66</v>
       </c>
@@ -30203,7 +30353,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="670" spans="1:8">
+    <row r="670" spans="1:7">
       <c r="A670" t="s">
         <v>66</v>
       </c>
@@ -30246,7 +30396,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="672" spans="1:8">
+    <row r="672" spans="1:7">
       <c r="A672" t="s">
         <v>66</v>
       </c>
@@ -30306,7 +30456,7 @@
         <v>303009</v>
       </c>
     </row>
-    <row r="675" spans="1:7">
+    <row r="675" spans="1:5">
       <c r="A675" t="s">
         <v>67</v>
       </c>
@@ -30583,7 +30733,7 @@
         <v>305013</v>
       </c>
     </row>
-    <row r="689" spans="1:8">
+    <row r="689" spans="1:7">
       <c r="A689" t="s">
         <v>67</v>
       </c>
@@ -30603,7 +30753,7 @@
         <v>305014</v>
       </c>
     </row>
-    <row r="690" spans="1:8">
+    <row r="690" spans="1:7">
       <c r="A690" t="s">
         <v>67</v>
       </c>
@@ -30623,7 +30773,7 @@
         <v>305015</v>
       </c>
     </row>
-    <row r="691" spans="1:8">
+    <row r="691" spans="1:7">
       <c r="A691" t="s">
         <v>67</v>
       </c>
@@ -30643,7 +30793,7 @@
         <v>305016</v>
       </c>
     </row>
-    <row r="692" spans="1:8">
+    <row r="692" spans="1:7">
       <c r="A692" t="s">
         <v>67</v>
       </c>
@@ -30663,7 +30813,7 @@
         <v>305017</v>
       </c>
     </row>
-    <row r="693" spans="1:8">
+    <row r="693" spans="1:7">
       <c r="A693" t="s">
         <v>67</v>
       </c>
@@ -30683,7 +30833,7 @@
         <v>305018</v>
       </c>
     </row>
-    <row r="694" spans="1:8">
+    <row r="694" spans="1:7">
       <c r="A694" t="s">
         <v>67</v>
       </c>
@@ -30703,7 +30853,7 @@
         <v>305019</v>
       </c>
     </row>
-    <row r="695" spans="1:8">
+    <row r="695" spans="1:7">
       <c r="A695" t="s">
         <v>67</v>
       </c>
@@ -30723,7 +30873,7 @@
         <v>305020</v>
       </c>
     </row>
-    <row r="696" spans="1:8">
+    <row r="696" spans="1:7">
       <c r="A696" t="s">
         <v>67</v>
       </c>
@@ -30743,7 +30893,7 @@
         <v>305021</v>
       </c>
     </row>
-    <row r="697" spans="1:8">
+    <row r="697" spans="1:5">
       <c r="A697" t="s">
         <v>68</v>
       </c>
@@ -30760,7 +30910,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="698" spans="1:8">
+    <row r="698" spans="1:7">
       <c r="A698" t="s">
         <v>68</v>
       </c>
@@ -30780,7 +30930,7 @@
         <v>308000</v>
       </c>
     </row>
-    <row r="699" spans="1:8">
+    <row r="699" spans="1:7">
       <c r="A699" t="s">
         <v>68</v>
       </c>
@@ -30800,7 +30950,7 @@
         <v>308001</v>
       </c>
     </row>
-    <row r="700" spans="1:8">
+    <row r="700" spans="1:7">
       <c r="A700" t="s">
         <v>68</v>
       </c>
@@ -30820,7 +30970,7 @@
         <v>308002</v>
       </c>
     </row>
-    <row r="701" spans="1:8">
+    <row r="701" spans="1:7">
       <c r="A701" t="s">
         <v>68</v>
       </c>
@@ -30840,7 +30990,7 @@
         <v>308003</v>
       </c>
     </row>
-    <row r="702" spans="1:8">
+    <row r="702" spans="1:7">
       <c r="A702" t="s">
         <v>68</v>
       </c>
@@ -30860,7 +31010,7 @@
         <v>308004</v>
       </c>
     </row>
-    <row r="703" spans="1:8">
+    <row r="703" spans="1:7">
       <c r="A703" t="s">
         <v>68</v>
       </c>
@@ -30903,7 +31053,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="705" spans="1:8">
+    <row r="705" spans="1:7">
       <c r="A705" t="s">
         <v>68</v>
       </c>
@@ -30923,7 +31073,7 @@
         <v>308007</v>
       </c>
     </row>
-    <row r="706" spans="1:8">
+    <row r="706" spans="1:7">
       <c r="A706" t="s">
         <v>68</v>
       </c>
@@ -30966,7 +31116,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="708" spans="1:8">
+    <row r="708" spans="1:7">
       <c r="A708" t="s">
         <v>68</v>
       </c>
@@ -30989,7 +31139,7 @@
         <v>308010</v>
       </c>
     </row>
-    <row r="709" spans="1:8">
+    <row r="709" spans="1:7">
       <c r="A709" t="s">
         <v>68</v>
       </c>
@@ -31012,7 +31162,7 @@
         <v>308011</v>
       </c>
     </row>
-    <row r="710" spans="1:8">
+    <row r="710" spans="1:7">
       <c r="A710" t="s">
         <v>68</v>
       </c>
@@ -31032,7 +31182,7 @@
         <v>308012</v>
       </c>
     </row>
-    <row r="711" spans="1:8">
+    <row r="711" spans="1:7">
       <c r="A711" t="s">
         <v>68</v>
       </c>
@@ -31052,7 +31202,7 @@
         <v>308013</v>
       </c>
     </row>
-    <row r="712" spans="1:8">
+    <row r="712" spans="1:7">
       <c r="A712" t="s">
         <v>68</v>
       </c>
@@ -31072,7 +31222,7 @@
         <v>308014</v>
       </c>
     </row>
-    <row r="713" spans="1:8">
+    <row r="713" spans="1:5">
       <c r="A713" t="s">
         <v>69</v>
       </c>
@@ -31089,7 +31239,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="714" spans="1:8">
+    <row r="714" spans="1:7">
       <c r="A714" t="s">
         <v>69</v>
       </c>
@@ -31109,7 +31259,7 @@
         <v>309000</v>
       </c>
     </row>
-    <row r="715" spans="1:8">
+    <row r="715" spans="1:7">
       <c r="A715" t="s">
         <v>69</v>
       </c>
@@ -31132,7 +31282,7 @@
         <v>309001</v>
       </c>
     </row>
-    <row r="716" spans="1:8">
+    <row r="716" spans="1:7">
       <c r="A716" t="s">
         <v>69</v>
       </c>
@@ -31152,7 +31302,7 @@
         <v>309002</v>
       </c>
     </row>
-    <row r="717" spans="1:8">
+    <row r="717" spans="1:7">
       <c r="A717" t="s">
         <v>69</v>
       </c>
@@ -31172,7 +31322,7 @@
         <v>309003</v>
       </c>
     </row>
-    <row r="718" spans="1:8">
+    <row r="718" spans="1:7">
       <c r="A718" t="s">
         <v>69</v>
       </c>
@@ -31238,7 +31388,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="721" spans="1:8">
+    <row r="721" spans="1:7">
       <c r="A721" t="s">
         <v>69</v>
       </c>
@@ -31258,7 +31408,7 @@
         <v>309007</v>
       </c>
     </row>
-    <row r="722" spans="1:8">
+    <row r="722" spans="1:7">
       <c r="A722" t="s">
         <v>69</v>
       </c>
@@ -31278,7 +31428,7 @@
         <v>309008</v>
       </c>
     </row>
-    <row r="723" spans="1:8">
+    <row r="723" spans="1:7">
       <c r="A723" t="s">
         <v>69</v>
       </c>
@@ -31298,7 +31448,7 @@
         <v>309009</v>
       </c>
     </row>
-    <row r="724" spans="1:8">
+    <row r="724" spans="1:7">
       <c r="A724" t="s">
         <v>69</v>
       </c>
@@ -31318,7 +31468,7 @@
         <v>309010</v>
       </c>
     </row>
-    <row r="725" spans="1:8">
+    <row r="725" spans="1:5">
       <c r="A725" t="s">
         <v>70</v>
       </c>
@@ -31335,7 +31485,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="726" spans="1:8">
+    <row r="726" spans="1:7">
       <c r="A726" t="s">
         <v>70</v>
       </c>
@@ -31358,7 +31508,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="727" spans="1:8">
+    <row r="727" spans="1:7">
       <c r="A727" t="s">
         <v>70</v>
       </c>
@@ -31608,7 +31758,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="738" spans="1:8">
+    <row r="738" spans="1:7">
       <c r="A738" t="s">
         <v>70</v>
       </c>
@@ -31628,7 +31778,7 @@
         <v>310012</v>
       </c>
     </row>
-    <row r="739" spans="1:8">
+    <row r="739" spans="1:5">
       <c r="A739" t="s">
         <v>71</v>
       </c>
@@ -31645,7 +31795,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="740" spans="1:8">
+    <row r="740" spans="1:7">
       <c r="A740" t="s">
         <v>71</v>
       </c>
@@ -32496,7 +32646,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="777" spans="1:8">
+    <row r="777" spans="1:5">
       <c r="A777" t="s">
         <v>74</v>
       </c>
@@ -32513,7 +32663,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="778" spans="1:8">
+    <row r="778" spans="1:7">
       <c r="A778" t="s">
         <v>74</v>
       </c>
@@ -32536,7 +32686,7 @@
         <v>318000</v>
       </c>
     </row>
-    <row r="779" spans="1:8">
+    <row r="779" spans="1:7">
       <c r="A779" t="s">
         <v>74</v>
       </c>
@@ -32556,7 +32706,7 @@
         <v>318001</v>
       </c>
     </row>
-    <row r="780" spans="1:8">
+    <row r="780" spans="1:7">
       <c r="A780" t="s">
         <v>74</v>
       </c>
@@ -32576,7 +32726,7 @@
         <v>318003</v>
       </c>
     </row>
-    <row r="781" spans="1:8">
+    <row r="781" spans="1:7">
       <c r="A781" t="s">
         <v>74</v>
       </c>
@@ -32665,7 +32815,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="785" spans="1:8">
+    <row r="785" spans="1:7">
       <c r="A785" t="s">
         <v>74</v>
       </c>
@@ -32823,7 +32973,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="792" spans="1:8">
+    <row r="792" spans="1:7">
       <c r="A792" t="s">
         <v>74</v>
       </c>
@@ -32843,7 +32993,7 @@
         <v>318007</v>
       </c>
     </row>
-    <row r="793" spans="1:8">
+    <row r="793" spans="1:7">
       <c r="A793" t="s">
         <v>74</v>
       </c>
@@ -32863,7 +33013,7 @@
         <v>318008</v>
       </c>
     </row>
-    <row r="794" spans="1:8">
+    <row r="794" spans="1:5">
       <c r="A794" t="s">
         <v>75</v>
       </c>
@@ -32880,7 +33030,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="795" spans="1:8">
+    <row r="795" spans="1:7">
       <c r="A795" t="s">
         <v>75</v>
       </c>
@@ -32903,7 +33053,7 @@
         <v>322000</v>
       </c>
     </row>
-    <row r="796" spans="1:8">
+    <row r="796" spans="1:7">
       <c r="A796" t="s">
         <v>75</v>
       </c>
@@ -33935,7 +34085,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="841" spans="1:8">
+    <row r="841" spans="1:7">
       <c r="A841" t="s">
         <v>75</v>
       </c>
@@ -33955,7 +34105,7 @@
         <v>322016</v>
       </c>
     </row>
-    <row r="842" spans="1:8">
+    <row r="842" spans="1:5">
       <c r="A842" t="s">
         <v>73</v>
       </c>
@@ -33972,7 +34122,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="843" spans="1:8">
+    <row r="843" spans="1:7">
       <c r="A843" t="s">
         <v>73</v>
       </c>
@@ -33995,7 +34145,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="844" spans="1:8">
+    <row r="844" spans="1:7">
       <c r="A844" t="s">
         <v>73</v>
       </c>
@@ -34107,7 +34257,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="849" spans="1:8">
+    <row r="849" spans="1:7">
       <c r="A849" t="s">
         <v>73</v>
       </c>
@@ -34127,7 +34277,7 @@
         <v>324006</v>
       </c>
     </row>
-    <row r="850" spans="1:8">
+    <row r="850" spans="1:7">
       <c r="A850" t="s">
         <v>73</v>
       </c>
@@ -34147,7 +34297,7 @@
         <v>324007</v>
       </c>
     </row>
-    <row r="851" spans="1:8">
+    <row r="851" spans="1:5">
       <c r="A851" t="s">
         <v>72</v>
       </c>
@@ -34164,7 +34314,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="852" spans="1:8">
+    <row r="852" spans="1:7">
       <c r="A852" t="s">
         <v>72</v>
       </c>
@@ -34184,7 +34334,7 @@
         <v>328000</v>
       </c>
     </row>
-    <row r="853" spans="1:8">
+    <row r="853" spans="1:7">
       <c r="A853" t="s">
         <v>72</v>
       </c>
@@ -34207,7 +34357,7 @@
         <v>328001</v>
       </c>
     </row>
-    <row r="854" spans="1:8">
+    <row r="854" spans="1:7">
       <c r="A854" t="s">
         <v>72</v>
       </c>
@@ -34319,7 +34469,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="859" spans="1:8">
+    <row r="859" spans="1:7">
       <c r="A859" t="s">
         <v>72</v>
       </c>
@@ -34339,7 +34489,7 @@
         <v>328007</v>
       </c>
     </row>
-    <row r="860" spans="1:8">
+    <row r="860" spans="1:5">
       <c r="A860" t="s">
         <v>121</v>
       </c>
@@ -34356,7 +34506,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="861" spans="1:8">
+    <row r="861" spans="1:7">
       <c r="A861" t="s">
         <v>121</v>
       </c>
@@ -34379,7 +34529,7 @@
         <v>347001</v>
       </c>
     </row>
-    <row r="862" spans="1:8">
+    <row r="862" spans="1:7">
       <c r="A862" t="s">
         <v>121</v>
       </c>
@@ -34399,7 +34549,7 @@
         <v>347002</v>
       </c>
     </row>
-    <row r="863" spans="1:8">
+    <row r="863" spans="1:7">
       <c r="A863" t="s">
         <v>121</v>
       </c>
@@ -34442,7 +34592,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="865" spans="1:8">
+    <row r="865" spans="1:7">
       <c r="A865" t="s">
         <v>121</v>
       </c>
@@ -34531,7 +34681,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="869" spans="1:8">
+    <row r="869" spans="1:7">
       <c r="A869" t="s">
         <v>121</v>
       </c>
@@ -34551,7 +34701,7 @@
         <v>347009</v>
       </c>
     </row>
-    <row r="870" spans="1:8">
+    <row r="870" spans="1:5">
       <c r="A870" t="s">
         <v>78</v>
       </c>
@@ -34568,7 +34718,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="871" spans="1:8">
+    <row r="871" spans="1:7">
       <c r="A871" t="s">
         <v>78</v>
       </c>
@@ -34588,7 +34738,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="872" spans="1:8">
+    <row r="872" spans="1:7">
       <c r="A872" t="s">
         <v>78</v>
       </c>
@@ -34608,7 +34758,7 @@
         <v>750011</v>
       </c>
     </row>
-    <row r="873" spans="1:8">
+    <row r="873" spans="1:7">
       <c r="A873" t="s">
         <v>78</v>
       </c>
@@ -34628,7 +34778,7 @@
         <v>750001</v>
       </c>
     </row>
-    <row r="874" spans="1:8">
+    <row r="874" spans="1:7">
       <c r="A874" t="s">
         <v>78</v>
       </c>
@@ -34648,7 +34798,7 @@
         <v>750002</v>
       </c>
     </row>
-    <row r="875" spans="1:8">
+    <row r="875" spans="1:7">
       <c r="A875" t="s">
         <v>78</v>
       </c>
@@ -34668,7 +34818,7 @@
         <v>750003</v>
       </c>
     </row>
-    <row r="876" spans="1:8">
+    <row r="876" spans="1:7">
       <c r="A876" t="s">
         <v>78</v>
       </c>
@@ -34688,7 +34838,7 @@
         <v>750004</v>
       </c>
     </row>
-    <row r="877" spans="1:8">
+    <row r="877" spans="1:7">
       <c r="A877" t="s">
         <v>78</v>
       </c>
@@ -34708,7 +34858,7 @@
         <v>750005</v>
       </c>
     </row>
-    <row r="878" spans="1:8">
+    <row r="878" spans="1:7">
       <c r="A878" t="s">
         <v>78</v>
       </c>
@@ -34728,7 +34878,7 @@
         <v>750006</v>
       </c>
     </row>
-    <row r="879" spans="1:8">
+    <row r="879" spans="1:7">
       <c r="A879" t="s">
         <v>78</v>
       </c>
@@ -34748,7 +34898,7 @@
         <v>750007</v>
       </c>
     </row>
-    <row r="880" spans="1:8">
+    <row r="880" spans="1:7">
       <c r="A880" t="s">
         <v>78</v>
       </c>
@@ -34768,7 +34918,7 @@
         <v>750008</v>
       </c>
     </row>
-    <row r="881" spans="1:8">
+    <row r="881" spans="1:7">
       <c r="A881" t="s">
         <v>78</v>
       </c>
@@ -34788,7 +34938,7 @@
         <v>750009</v>
       </c>
     </row>
-    <row r="882" spans="1:8">
+    <row r="882" spans="1:7">
       <c r="A882" t="s">
         <v>78</v>
       </c>
@@ -34808,7 +34958,7 @@
         <v>750010</v>
       </c>
     </row>
-    <row r="883" spans="1:8">
+    <row r="883" spans="1:5">
       <c r="A883" t="s">
         <v>80</v>
       </c>
@@ -34825,7 +34975,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="884" spans="1:8">
+    <row r="884" spans="1:7">
       <c r="A884" t="s">
         <v>80</v>
       </c>
@@ -34845,7 +34995,7 @@
         <v>752000</v>
       </c>
     </row>
-    <row r="885" spans="1:8">
+    <row r="885" spans="1:7">
       <c r="A885" t="s">
         <v>80</v>
       </c>
@@ -34868,7 +35018,7 @@
         <v>752001</v>
       </c>
     </row>
-    <row r="886" spans="1:8">
+    <row r="886" spans="1:7">
       <c r="A886" t="s">
         <v>80</v>
       </c>
@@ -34891,7 +35041,7 @@
         <v>752002</v>
       </c>
     </row>
-    <row r="887" spans="1:8">
+    <row r="887" spans="1:7">
       <c r="A887" t="s">
         <v>80</v>
       </c>
@@ -34911,7 +35061,7 @@
         <v>752003</v>
       </c>
     </row>
-    <row r="888" spans="1:8">
+    <row r="888" spans="1:7">
       <c r="A888" t="s">
         <v>80</v>
       </c>
@@ -34931,7 +35081,7 @@
         <v>752004</v>
       </c>
     </row>
-    <row r="889" spans="1:8">
+    <row r="889" spans="1:7">
       <c r="A889" t="s">
         <v>80</v>
       </c>
@@ -34951,7 +35101,7 @@
         <v>752005</v>
       </c>
     </row>
-    <row r="890" spans="1:8">
+    <row r="890" spans="1:5">
       <c r="A890" t="s">
         <v>81</v>
       </c>
@@ -34968,7 +35118,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="891" spans="1:8">
+    <row r="891" spans="1:7">
       <c r="A891" t="s">
         <v>81</v>
       </c>
@@ -34991,7 +35141,7 @@
         <v>800001</v>
       </c>
     </row>
-    <row r="892" spans="1:8">
+    <row r="892" spans="1:7">
       <c r="A892" t="s">
         <v>81</v>
       </c>
@@ -35011,7 +35161,7 @@
         <v>800002</v>
       </c>
     </row>
-    <row r="893" spans="1:8">
+    <row r="893" spans="1:7">
       <c r="A893" t="s">
         <v>81</v>
       </c>
@@ -35422,7 +35572,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="911" spans="1:8">
+    <row r="911" spans="1:5">
       <c r="A911" t="s">
         <v>83</v>
       </c>
@@ -35439,7 +35589,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="912" spans="1:8">
+    <row r="912" spans="1:7">
       <c r="A912" t="s">
         <v>83</v>
       </c>
@@ -35462,7 +35612,7 @@
         <v>802001</v>
       </c>
     </row>
-    <row r="913" spans="1:8">
+    <row r="913" spans="1:7">
       <c r="A913" t="s">
         <v>83</v>
       </c>
@@ -35482,7 +35632,7 @@
         <v>802002</v>
       </c>
     </row>
-    <row r="914" spans="1:8">
+    <row r="914" spans="1:7">
       <c r="A914" t="s">
         <v>83</v>
       </c>
@@ -39688,7 +39838,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1097" spans="1:8">
+    <row r="1097" spans="1:5">
       <c r="A1097" t="s">
         <v>84</v>
       </c>
@@ -39705,7 +39855,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1098" spans="1:8">
+    <row r="1098" spans="1:7">
       <c r="A1098" t="s">
         <v>84</v>
       </c>
@@ -39728,7 +39878,7 @@
         <v>803001</v>
       </c>
     </row>
-    <row r="1099" spans="1:8">
+    <row r="1099" spans="1:7">
       <c r="A1099" t="s">
         <v>84</v>
       </c>
@@ -39748,7 +39898,7 @@
         <v>803002</v>
       </c>
     </row>
-    <row r="1100" spans="1:8">
+    <row r="1100" spans="1:7">
       <c r="A1100" t="s">
         <v>84</v>
       </c>
@@ -42666,7 +42816,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1227" spans="1:8">
+    <row r="1227" spans="1:5">
       <c r="A1227" t="s">
         <v>85</v>
       </c>
@@ -42683,7 +42833,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1228" spans="1:8">
+    <row r="1228" spans="1:7">
       <c r="A1228" t="s">
         <v>85</v>
       </c>
@@ -42706,7 +42856,7 @@
         <v>804001</v>
       </c>
     </row>
-    <row r="1229" spans="1:8">
+    <row r="1229" spans="1:7">
       <c r="A1229" t="s">
         <v>85</v>
       </c>
@@ -42726,7 +42876,7 @@
         <v>804002</v>
       </c>
     </row>
-    <row r="1230" spans="1:8">
+    <row r="1230" spans="1:7">
       <c r="A1230" t="s">
         <v>85</v>
       </c>
@@ -45000,7 +45150,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1329" spans="1:8">
+    <row r="1329" spans="1:5">
       <c r="A1329" t="s">
         <v>86</v>
       </c>
@@ -45017,7 +45167,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1330" spans="1:8">
+    <row r="1330" spans="1:7">
       <c r="A1330" t="s">
         <v>86</v>
       </c>
@@ -45040,7 +45190,7 @@
         <v>805001</v>
       </c>
     </row>
-    <row r="1331" spans="1:8">
+    <row r="1331" spans="1:7">
       <c r="A1331" t="s">
         <v>86</v>
       </c>
@@ -45060,7 +45210,7 @@
         <v>805002</v>
       </c>
     </row>
-    <row r="1332" spans="1:8">
+    <row r="1332" spans="1:7">
       <c r="A1332" t="s">
         <v>86</v>
       </c>
@@ -47196,7 +47346,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1425" spans="1:8">
+    <row r="1425" spans="1:5">
       <c r="A1425" t="s">
         <v>87</v>
       </c>
@@ -47213,7 +47363,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1426" spans="1:8">
+    <row r="1426" spans="1:7">
       <c r="A1426" t="s">
         <v>87</v>
       </c>
@@ -47236,7 +47386,7 @@
         <v>807001</v>
       </c>
     </row>
-    <row r="1427" spans="1:8">
+    <row r="1427" spans="1:7">
       <c r="A1427" t="s">
         <v>87</v>
       </c>
@@ -47256,7 +47406,7 @@
         <v>807002</v>
       </c>
     </row>
-    <row r="1428" spans="1:8">
+    <row r="1428" spans="1:7">
       <c r="A1428" t="s">
         <v>87</v>
       </c>
@@ -50588,7 +50738,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1573" spans="1:8">
+    <row r="1573" spans="1:5">
       <c r="A1573" t="s">
         <v>88</v>
       </c>
@@ -50605,7 +50755,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1574" spans="1:8">
+    <row r="1574" spans="1:7">
       <c r="A1574" t="s">
         <v>88</v>
       </c>
@@ -50628,7 +50778,7 @@
         <v>808001</v>
       </c>
     </row>
-    <row r="1575" spans="1:8">
+    <row r="1575" spans="1:7">
       <c r="A1575" t="s">
         <v>88</v>
       </c>
@@ -50648,7 +50798,7 @@
         <v>808002</v>
       </c>
     </row>
-    <row r="1576" spans="1:8">
+    <row r="1576" spans="1:7">
       <c r="A1576" t="s">
         <v>88</v>
       </c>
@@ -54118,7 +54268,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1727" spans="1:8">
+    <row r="1727" spans="1:5">
       <c r="A1727" t="s">
         <v>89</v>
       </c>
@@ -54135,7 +54285,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1728" spans="1:8">
+    <row r="1728" spans="1:7">
       <c r="A1728" t="s">
         <v>89</v>
       </c>
@@ -54158,7 +54308,7 @@
         <v>809001</v>
       </c>
     </row>
-    <row r="1729" spans="1:8">
+    <row r="1729" spans="1:7">
       <c r="A1729" t="s">
         <v>89</v>
       </c>
@@ -54178,7 +54328,7 @@
         <v>809002</v>
       </c>
     </row>
-    <row r="1730" spans="1:8">
+    <row r="1730" spans="1:7">
       <c r="A1730" t="s">
         <v>89</v>
       </c>
@@ -54520,7 +54670,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1745" spans="1:8">
+    <row r="1745" spans="1:5">
       <c r="A1745" t="s">
         <v>90</v>
       </c>
@@ -54537,7 +54687,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1746" spans="1:8">
+    <row r="1746" spans="1:7">
       <c r="A1746" t="s">
         <v>90</v>
       </c>
@@ -54560,7 +54710,7 @@
         <v>810001</v>
       </c>
     </row>
-    <row r="1747" spans="1:8">
+    <row r="1747" spans="1:7">
       <c r="A1747" t="s">
         <v>90</v>
       </c>
@@ -54580,7 +54730,7 @@
         <v>810002</v>
       </c>
     </row>
-    <row r="1748" spans="1:8">
+    <row r="1748" spans="1:7">
       <c r="A1748" t="s">
         <v>90</v>
       </c>
@@ -55612,7 +55762,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1793" spans="1:8">
+    <row r="1793" spans="1:5">
       <c r="A1793" t="s">
         <v>92</v>
       </c>
@@ -55629,7 +55779,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1794" spans="1:8">
+    <row r="1794" spans="1:7">
       <c r="A1794" t="s">
         <v>92</v>
       </c>
@@ -55649,7 +55799,7 @@
         <v>812001</v>
       </c>
     </row>
-    <row r="1795" spans="1:8">
+    <row r="1795" spans="1:7">
       <c r="A1795" t="s">
         <v>92</v>
       </c>
@@ -55669,7 +55819,7 @@
         <v>812002</v>
       </c>
     </row>
-    <row r="1796" spans="1:8">
+    <row r="1796" spans="1:7">
       <c r="A1796" t="s">
         <v>92</v>
       </c>
@@ -55689,7 +55839,7 @@
         <v>812003</v>
       </c>
     </row>
-    <row r="1797" spans="1:8">
+    <row r="1797" spans="1:7">
       <c r="A1797" t="s">
         <v>92</v>
       </c>
@@ -55758,7 +55908,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1800" spans="1:8">
+    <row r="1800" spans="1:5">
       <c r="A1800" t="s">
         <v>91</v>
       </c>
@@ -55775,7 +55925,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1801" spans="1:8">
+    <row r="1801" spans="1:7">
       <c r="A1801" t="s">
         <v>91</v>
       </c>
@@ -55798,7 +55948,7 @@
         <v>814001</v>
       </c>
     </row>
-    <row r="1802" spans="1:8">
+    <row r="1802" spans="1:7">
       <c r="A1802" t="s">
         <v>91</v>
       </c>
@@ -55818,7 +55968,7 @@
         <v>814002</v>
       </c>
     </row>
-    <row r="1803" spans="1:8">
+    <row r="1803" spans="1:7">
       <c r="A1803" t="s">
         <v>91</v>
       </c>
@@ -57632,7 +57782,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1882" spans="1:8">
+    <row r="1882" spans="1:5">
       <c r="A1882" t="s">
         <v>94</v>
       </c>
@@ -57649,7 +57799,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1883" spans="1:8">
+    <row r="1883" spans="1:7">
       <c r="A1883" t="s">
         <v>94</v>
       </c>
@@ -57672,7 +57822,7 @@
         <v>760001</v>
       </c>
     </row>
-    <row r="1884" spans="1:8">
+    <row r="1884" spans="1:7">
       <c r="A1884" t="s">
         <v>94</v>
       </c>
@@ -57692,7 +57842,7 @@
         <v>760002</v>
       </c>
     </row>
-    <row r="1885" spans="1:8">
+    <row r="1885" spans="1:7">
       <c r="A1885" t="s">
         <v>94</v>
       </c>
@@ -57712,7 +57862,7 @@
         <v>760003</v>
       </c>
     </row>
-    <row r="1886" spans="1:8">
+    <row r="1886" spans="1:7">
       <c r="A1886" t="s">
         <v>94</v>
       </c>
@@ -57755,7 +57905,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="1888" spans="1:8">
+    <row r="1888" spans="1:7">
       <c r="A1888" t="s">
         <v>94</v>
       </c>
@@ -57835,7 +57985,7 @@
         <v>760009</v>
       </c>
     </row>
-    <row r="1892" spans="1:7">
+    <row r="1892" spans="1:5">
       <c r="A1892" t="s">
         <v>100</v>
       </c>
@@ -58095,7 +58245,7 @@
         <v>703012</v>
       </c>
     </row>
-    <row r="1905" spans="1:8">
+    <row r="1905" spans="1:7">
       <c r="A1905" t="s">
         <v>100</v>
       </c>
@@ -58138,7 +58288,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="1907" spans="1:8">
+    <row r="1907" spans="1:7">
       <c r="A1907" t="s">
         <v>100</v>
       </c>
@@ -58181,7 +58331,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="1909" spans="1:8">
+    <row r="1909" spans="1:7">
       <c r="A1909" t="s">
         <v>100</v>
       </c>
@@ -58201,7 +58351,7 @@
         <v>703017</v>
       </c>
     </row>
-    <row r="1910" spans="1:8">
+    <row r="1910" spans="1:7">
       <c r="A1910" t="s">
         <v>100</v>
       </c>
@@ -58221,7 +58371,7 @@
         <v>703018</v>
       </c>
     </row>
-    <row r="1911" spans="1:8">
+    <row r="1911" spans="1:7">
       <c r="A1911" t="s">
         <v>100</v>
       </c>
@@ -58264,7 +58414,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="1913" spans="1:8">
+    <row r="1913" spans="1:7">
       <c r="A1913" t="s">
         <v>100</v>
       </c>
@@ -58307,7 +58457,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="1915" spans="1:8">
+    <row r="1915" spans="1:7">
       <c r="A1915" t="s">
         <v>100</v>
       </c>
@@ -58327,7 +58477,7 @@
         <v>703023</v>
       </c>
     </row>
-    <row r="1916" spans="1:8">
+    <row r="1916" spans="1:7">
       <c r="A1916" t="s">
         <v>100</v>
       </c>
@@ -58347,7 +58497,7 @@
         <v>703024</v>
       </c>
     </row>
-    <row r="1917" spans="1:8">
+    <row r="1917" spans="1:7">
       <c r="A1917" t="s">
         <v>100</v>
       </c>
@@ -58367,7 +58517,7 @@
         <v>703025</v>
       </c>
     </row>
-    <row r="1918" spans="1:8">
+    <row r="1918" spans="1:7">
       <c r="A1918" t="s">
         <v>100</v>
       </c>
@@ -58387,7 +58537,7 @@
         <v>703026</v>
       </c>
     </row>
-    <row r="1919" spans="1:8">
+    <row r="1919" spans="1:7">
       <c r="A1919" t="s">
         <v>100</v>
       </c>
@@ -58407,7 +58557,7 @@
         <v>703027</v>
       </c>
     </row>
-    <row r="1920" spans="1:8">
+    <row r="1920" spans="1:7">
       <c r="A1920" t="s">
         <v>100</v>
       </c>
@@ -58427,7 +58577,7 @@
         <v>703028</v>
       </c>
     </row>
-    <row r="1921" spans="1:8">
+    <row r="1921" spans="1:7">
       <c r="A1921" t="s">
         <v>100</v>
       </c>
@@ -58447,7 +58597,7 @@
         <v>703029</v>
       </c>
     </row>
-    <row r="1922" spans="1:8">
+    <row r="1922" spans="1:7">
       <c r="A1922" t="s">
         <v>100</v>
       </c>
@@ -58467,7 +58617,7 @@
         <v>703030</v>
       </c>
     </row>
-    <row r="1923" spans="1:8">
+    <row r="1923" spans="1:5">
       <c r="A1923" t="s">
         <v>101</v>
       </c>
@@ -58484,7 +58634,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1924" spans="1:8">
+    <row r="1924" spans="1:7">
       <c r="A1924" t="s">
         <v>101</v>
       </c>
@@ -58783,7 +58933,7 @@
         <v>3301</v>
       </c>
     </row>
-    <row r="1937" spans="1:8">
+    <row r="1937" spans="1:5">
       <c r="A1937" t="s">
         <v>102</v>
       </c>
@@ -58800,7 +58950,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1938" spans="1:8">
+    <row r="1938" spans="1:7">
       <c r="A1938" t="s">
         <v>102</v>
       </c>
@@ -58820,7 +58970,7 @@
         <v>710001</v>
       </c>
     </row>
-    <row r="1939" spans="1:8">
+    <row r="1939" spans="1:7">
       <c r="A1939" t="s">
         <v>102</v>
       </c>
@@ -58866,7 +59016,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1941" spans="1:8">
+    <row r="1941" spans="1:7">
       <c r="A1941" t="s">
         <v>102</v>
       </c>
@@ -58886,7 +59036,7 @@
         <v>710004</v>
       </c>
     </row>
-    <row r="1942" spans="1:8">
+    <row r="1942" spans="1:5">
       <c r="A1942" t="s">
         <v>104</v>
       </c>
@@ -58903,7 +59053,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1943" spans="1:8">
+    <row r="1943" spans="1:7">
       <c r="A1943" t="s">
         <v>104</v>
       </c>
@@ -58926,7 +59076,7 @@
         <v>705001</v>
       </c>
     </row>
-    <row r="1944" spans="1:8">
+    <row r="1944" spans="1:7">
       <c r="A1944" t="s">
         <v>104</v>
       </c>
@@ -59061,7 +59211,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="1950" spans="1:8">
+    <row r="1950" spans="1:5">
       <c r="A1950" t="s">
         <v>105</v>
       </c>
@@ -59078,7 +59228,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1951" spans="1:8">
+    <row r="1951" spans="1:7">
       <c r="A1951" t="s">
         <v>105</v>
       </c>
@@ -59101,7 +59251,7 @@
         <v>706001</v>
       </c>
     </row>
-    <row r="1952" spans="1:8">
+    <row r="1952" spans="1:7">
       <c r="A1952" t="s">
         <v>105</v>
       </c>
@@ -59121,7 +59271,7 @@
         <v>706002</v>
       </c>
     </row>
-    <row r="1953" spans="1:8">
+    <row r="1953" spans="1:7">
       <c r="A1953" t="s">
         <v>105</v>
       </c>
@@ -59187,7 +59337,7 @@
         <v>3335</v>
       </c>
     </row>
-    <row r="1956" spans="1:8">
+    <row r="1956" spans="1:5">
       <c r="A1956" t="s">
         <v>106</v>
       </c>
@@ -59204,7 +59354,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1957" spans="1:8">
+    <row r="1957" spans="1:7">
       <c r="A1957" t="s">
         <v>106</v>
       </c>
@@ -59227,7 +59377,7 @@
         <v>707001</v>
       </c>
     </row>
-    <row r="1958" spans="1:8">
+    <row r="1958" spans="1:7">
       <c r="A1958" t="s">
         <v>106</v>
       </c>
@@ -59247,7 +59397,7 @@
         <v>707002</v>
       </c>
     </row>
-    <row r="1959" spans="1:8">
+    <row r="1959" spans="1:7">
       <c r="A1959" t="s">
         <v>106</v>
       </c>
@@ -59267,7 +59417,7 @@
         <v>707003</v>
       </c>
     </row>
-    <row r="1960" spans="1:8">
+    <row r="1960" spans="1:7">
       <c r="A1960" t="s">
         <v>106</v>
       </c>
@@ -59287,7 +59437,7 @@
         <v>707004</v>
       </c>
     </row>
-    <row r="1961" spans="1:8">
+    <row r="1961" spans="1:7">
       <c r="A1961" t="s">
         <v>106</v>
       </c>
@@ -59307,7 +59457,7 @@
         <v>707005</v>
       </c>
     </row>
-    <row r="1962" spans="1:8">
+    <row r="1962" spans="1:7">
       <c r="A1962" t="s">
         <v>106</v>
       </c>
@@ -59327,7 +59477,7 @@
         <v>707006</v>
       </c>
     </row>
-    <row r="1963" spans="1:8">
+    <row r="1963" spans="1:7">
       <c r="A1963" t="s">
         <v>106</v>
       </c>
@@ -59347,7 +59497,7 @@
         <v>707007</v>
       </c>
     </row>
-    <row r="1964" spans="1:8">
+    <row r="1964" spans="1:7">
       <c r="A1964" t="s">
         <v>106</v>
       </c>
@@ -59367,7 +59517,7 @@
         <v>707008</v>
       </c>
     </row>
-    <row r="1965" spans="1:8">
+    <row r="1965" spans="1:7">
       <c r="A1965" t="s">
         <v>106</v>
       </c>
@@ -59387,7 +59537,7 @@
         <v>707009</v>
       </c>
     </row>
-    <row r="1966" spans="1:8">
+    <row r="1966" spans="1:7">
       <c r="A1966" t="s">
         <v>106</v>
       </c>
@@ -59499,7 +59649,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="1971" spans="1:8">
+    <row r="1971" spans="1:5">
       <c r="A1971" t="s">
         <v>96</v>
       </c>
@@ -59516,7 +59666,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1972" spans="1:8">
+    <row r="1972" spans="1:7">
       <c r="A1972" t="s">
         <v>96</v>
       </c>
@@ -59536,7 +59686,7 @@
         <v>708001</v>
       </c>
     </row>
-    <row r="1973" spans="1:8">
+    <row r="1973" spans="1:7">
       <c r="A1973" t="s">
         <v>96</v>
       </c>
@@ -59559,7 +59709,7 @@
         <v>708002</v>
       </c>
     </row>
-    <row r="1974" spans="1:8">
+    <row r="1974" spans="1:7">
       <c r="A1974" t="s">
         <v>96</v>
       </c>
@@ -59579,7 +59729,7 @@
         <v>708003</v>
       </c>
     </row>
-    <row r="1975" spans="1:8">
+    <row r="1975" spans="1:7">
       <c r="A1975" t="s">
         <v>96</v>
       </c>
@@ -59599,7 +59749,7 @@
         <v>708004</v>
       </c>
     </row>
-    <row r="1976" spans="1:8">
+    <row r="1976" spans="1:7">
       <c r="A1976" t="s">
         <v>96</v>
       </c>
@@ -59619,7 +59769,7 @@
         <v>708005</v>
       </c>
     </row>
-    <row r="1977" spans="1:8">
+    <row r="1977" spans="1:7">
       <c r="A1977" t="s">
         <v>96</v>
       </c>
@@ -59639,7 +59789,7 @@
         <v>708006</v>
       </c>
     </row>
-    <row r="1978" spans="1:8">
+    <row r="1978" spans="1:7">
       <c r="A1978" t="s">
         <v>96</v>
       </c>
@@ -59659,7 +59809,7 @@
         <v>708007</v>
       </c>
     </row>
-    <row r="1979" spans="1:8">
+    <row r="1979" spans="1:7">
       <c r="A1979" t="s">
         <v>96</v>
       </c>
@@ -59679,7 +59829,7 @@
         <v>708008</v>
       </c>
     </row>
-    <row r="1980" spans="1:8">
+    <row r="1980" spans="1:7">
       <c r="A1980" t="s">
         <v>96</v>
       </c>
@@ -59699,7 +59849,7 @@
         <v>708009</v>
       </c>
     </row>
-    <row r="1981" spans="1:8">
+    <row r="1981" spans="1:7">
       <c r="A1981" t="s">
         <v>96</v>
       </c>
@@ -59719,7 +59869,7 @@
         <v>708010</v>
       </c>
     </row>
-    <row r="1982" spans="1:8">
+    <row r="1982" spans="1:5">
       <c r="A1982" t="s">
         <v>107</v>
       </c>
@@ -59736,7 +59886,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1983" spans="1:8">
+    <row r="1983" spans="1:7">
       <c r="A1983" t="s">
         <v>107</v>
       </c>
@@ -59756,7 +59906,7 @@
         <v>702001</v>
       </c>
     </row>
-    <row r="1984" spans="1:8">
+    <row r="1984" spans="1:7">
       <c r="A1984" t="s">
         <v>107</v>
       </c>
@@ -59776,7 +59926,7 @@
         <v>702002</v>
       </c>
     </row>
-    <row r="1985" spans="1:8">
+    <row r="1985" spans="1:7">
       <c r="A1985" t="s">
         <v>107</v>
       </c>
@@ -59796,7 +59946,7 @@
         <v>702003</v>
       </c>
     </row>
-    <row r="1986" spans="1:8">
+    <row r="1986" spans="1:7">
       <c r="A1986" t="s">
         <v>107</v>
       </c>
@@ -59839,7 +59989,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="1988" spans="1:8">
+    <row r="1988" spans="1:7">
       <c r="A1988" t="s">
         <v>107</v>
       </c>
@@ -59859,7 +60009,7 @@
         <v>702006</v>
       </c>
     </row>
-    <row r="1989" spans="1:8">
+    <row r="1989" spans="1:5">
       <c r="A1989" t="s">
         <v>103</v>
       </c>
@@ -59876,7 +60026,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1990" spans="1:8">
+    <row r="1990" spans="1:7">
       <c r="A1990" t="s">
         <v>103</v>
       </c>
@@ -59896,7 +60046,7 @@
         <v>701001</v>
       </c>
     </row>
-    <row r="1991" spans="1:8">
+    <row r="1991" spans="1:7">
       <c r="A1991" t="s">
         <v>103</v>
       </c>
@@ -59919,7 +60069,7 @@
         <v>701002</v>
       </c>
     </row>
-    <row r="1992" spans="1:8">
+    <row r="1992" spans="1:7">
       <c r="A1992" t="s">
         <v>103</v>
       </c>
@@ -59939,7 +60089,7 @@
         <v>701003</v>
       </c>
     </row>
-    <row r="1993" spans="1:8">
+    <row r="1993" spans="1:7">
       <c r="A1993" t="s">
         <v>103</v>
       </c>
@@ -59959,7 +60109,7 @@
         <v>701004</v>
       </c>
     </row>
-    <row r="1994" spans="1:8">
+    <row r="1994" spans="1:7">
       <c r="A1994" t="s">
         <v>103</v>
       </c>
@@ -60025,7 +60175,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="1997" spans="1:8">
+    <row r="1997" spans="1:7">
       <c r="A1997" t="s">
         <v>103</v>
       </c>
@@ -60045,7 +60195,7 @@
         <v>701008</v>
       </c>
     </row>
-    <row r="1998" spans="1:8">
+    <row r="1998" spans="1:5">
       <c r="A1998" t="s">
         <v>98</v>
       </c>
@@ -60062,7 +60212,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1999" spans="1:8">
+    <row r="1999" spans="1:7">
       <c r="A1999" t="s">
         <v>98</v>
       </c>
@@ -60085,7 +60235,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="2000" spans="1:8">
+    <row r="2000" spans="1:7">
       <c r="A2000" t="s">
         <v>98</v>
       </c>
@@ -60105,7 +60255,7 @@
         <v>700001</v>
       </c>
     </row>
-    <row r="2001" spans="1:8">
+    <row r="2001" spans="1:7">
       <c r="A2001" t="s">
         <v>98</v>
       </c>
@@ -60125,7 +60275,7 @@
         <v>700002</v>
       </c>
     </row>
-    <row r="2002" spans="1:8">
+    <row r="2002" spans="1:7">
       <c r="A2002" t="s">
         <v>98</v>
       </c>
@@ -60145,7 +60295,7 @@
         <v>700003</v>
       </c>
     </row>
-    <row r="2003" spans="1:8">
+    <row r="2003" spans="1:5">
       <c r="A2003" t="s">
         <v>108</v>
       </c>
@@ -60162,7 +60312,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2004" spans="1:8">
+    <row r="2004" spans="1:7">
       <c r="A2004" t="s">
         <v>108</v>
       </c>
@@ -60205,7 +60355,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2006" spans="1:8">
+    <row r="2006" spans="1:7">
       <c r="A2006" t="s">
         <v>108</v>
       </c>
@@ -60225,7 +60375,7 @@
         <v>502002</v>
       </c>
     </row>
-    <row r="2007" spans="1:8">
+    <row r="2007" spans="1:7">
       <c r="A2007" t="s">
         <v>108</v>
       </c>
@@ -60245,7 +60395,7 @@
         <v>502003</v>
       </c>
     </row>
-    <row r="2008" spans="1:8">
+    <row r="2008" spans="1:7">
       <c r="A2008" t="s">
         <v>108</v>
       </c>
@@ -60265,7 +60415,7 @@
         <v>502037</v>
       </c>
     </row>
-    <row r="2009" spans="1:8">
+    <row r="2009" spans="1:7">
       <c r="A2009" t="s">
         <v>108</v>
       </c>
@@ -60285,7 +60435,7 @@
         <v>502004</v>
       </c>
     </row>
-    <row r="2010" spans="1:8">
+    <row r="2010" spans="1:7">
       <c r="A2010" t="s">
         <v>108</v>
       </c>
@@ -60305,7 +60455,7 @@
         <v>502005</v>
       </c>
     </row>
-    <row r="2011" spans="1:8">
+    <row r="2011" spans="1:7">
       <c r="A2011" t="s">
         <v>108</v>
       </c>
@@ -60348,7 +60498,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2013" spans="1:8">
+    <row r="2013" spans="1:7">
       <c r="A2013" t="s">
         <v>108</v>
       </c>
@@ -60414,7 +60564,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2016" spans="1:8">
+    <row r="2016" spans="1:7">
       <c r="A2016" t="s">
         <v>108</v>
       </c>
@@ -60434,7 +60584,7 @@
         <v>502011</v>
       </c>
     </row>
-    <row r="2017" spans="1:8">
+    <row r="2017" spans="1:7">
       <c r="A2017" t="s">
         <v>108</v>
       </c>
@@ -60454,7 +60604,7 @@
         <v>502012</v>
       </c>
     </row>
-    <row r="2018" spans="1:8">
+    <row r="2018" spans="1:7">
       <c r="A2018" t="s">
         <v>108</v>
       </c>
@@ -60474,7 +60624,7 @@
         <v>502034</v>
       </c>
     </row>
-    <row r="2019" spans="1:8">
+    <row r="2019" spans="1:7">
       <c r="A2019" t="s">
         <v>108</v>
       </c>
@@ -60540,7 +60690,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2022" spans="1:8">
+    <row r="2022" spans="1:7">
       <c r="A2022" t="s">
         <v>108</v>
       </c>
@@ -60583,7 +60733,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2024" spans="1:8">
+    <row r="2024" spans="1:7">
       <c r="A2024" t="s">
         <v>108</v>
       </c>
@@ -60626,7 +60776,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2026" spans="1:8">
+    <row r="2026" spans="1:7">
       <c r="A2026" t="s">
         <v>108</v>
       </c>
@@ -60646,7 +60796,7 @@
         <v>502033</v>
       </c>
     </row>
-    <row r="2027" spans="1:8">
+    <row r="2027" spans="1:7">
       <c r="A2027" t="s">
         <v>108</v>
       </c>
@@ -60666,7 +60816,7 @@
         <v>502020</v>
       </c>
     </row>
-    <row r="2028" spans="1:8">
+    <row r="2028" spans="1:7">
       <c r="A2028" t="s">
         <v>108</v>
       </c>
@@ -60732,7 +60882,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="2031" spans="1:8">
+    <row r="2031" spans="1:7">
       <c r="A2031" t="s">
         <v>108</v>
       </c>
@@ -60752,7 +60902,7 @@
         <v>502024</v>
       </c>
     </row>
-    <row r="2032" spans="1:8">
+    <row r="2032" spans="1:7">
       <c r="A2032" t="s">
         <v>108</v>
       </c>
@@ -61252,7 +61402,7 @@
         <v>502055</v>
       </c>
     </row>
-    <row r="2057" spans="1:7">
+    <row r="2057" spans="1:5">
       <c r="A2057" t="s">
         <v>110</v>
       </c>
@@ -61412,7 +61562,7 @@
         <v>503006</v>
       </c>
     </row>
-    <row r="2065" spans="1:8">
+    <row r="2065" spans="1:7">
       <c r="A2065" t="s">
         <v>110</v>
       </c>
@@ -61432,7 +61582,7 @@
         <v>503007</v>
       </c>
     </row>
-    <row r="2066" spans="1:8">
+    <row r="2066" spans="1:7">
       <c r="A2066" t="s">
         <v>110</v>
       </c>
@@ -61452,7 +61602,7 @@
         <v>503008</v>
       </c>
     </row>
-    <row r="2067" spans="1:8">
+    <row r="2067" spans="1:5">
       <c r="A2067" t="s">
         <v>111</v>
       </c>
@@ -61469,7 +61619,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2068" spans="1:8">
+    <row r="2068" spans="1:7">
       <c r="A2068" t="s">
         <v>111</v>
       </c>
@@ -61489,7 +61639,7 @@
         <v>505001</v>
       </c>
     </row>
-    <row r="2069" spans="1:8">
+    <row r="2069" spans="1:7">
       <c r="A2069" t="s">
         <v>111</v>
       </c>
@@ -61509,7 +61659,7 @@
         <v>505002</v>
       </c>
     </row>
-    <row r="2070" spans="1:8">
+    <row r="2070" spans="1:7">
       <c r="A2070" t="s">
         <v>111</v>
       </c>
@@ -61598,7 +61748,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2074" spans="1:8">
+    <row r="2074" spans="1:7">
       <c r="A2074" t="s">
         <v>111</v>
       </c>
@@ -61618,7 +61768,7 @@
         <v>505007</v>
       </c>
     </row>
-    <row r="2075" spans="1:8">
+    <row r="2075" spans="1:7">
       <c r="A2075" t="s">
         <v>111</v>
       </c>
@@ -61638,7 +61788,7 @@
         <v>505008</v>
       </c>
     </row>
-    <row r="2076" spans="1:8">
+    <row r="2076" spans="1:7">
       <c r="A2076" t="s">
         <v>111</v>
       </c>
@@ -61658,7 +61808,7 @@
         <v>505009</v>
       </c>
     </row>
-    <row r="2077" spans="1:8">
+    <row r="2077" spans="1:5">
       <c r="A2077" t="s">
         <v>112</v>
       </c>
@@ -61675,7 +61825,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2078" spans="1:8">
+    <row r="2078" spans="1:7">
       <c r="A2078" t="s">
         <v>112</v>
       </c>
@@ -61695,7 +61845,7 @@
         <v>507000</v>
       </c>
     </row>
-    <row r="2079" spans="1:8">
+    <row r="2079" spans="1:7">
       <c r="A2079" t="s">
         <v>112</v>
       </c>
@@ -61718,7 +61868,7 @@
         <v>507001</v>
       </c>
     </row>
-    <row r="2080" spans="1:8">
+    <row r="2080" spans="1:7">
       <c r="A2080" t="s">
         <v>112</v>
       </c>
@@ -61878,7 +62028,7 @@
         <v>507009</v>
       </c>
     </row>
-    <row r="2088" spans="1:7">
+    <row r="2088" spans="1:5">
       <c r="A2088" t="s">
         <v>113</v>
       </c>
@@ -62098,7 +62248,7 @@
         <v>508009</v>
       </c>
     </row>
-    <row r="2099" spans="1:7">
+    <row r="2099" spans="1:5">
       <c r="A2099" t="s">
         <v>114</v>
       </c>
@@ -62198,7 +62348,7 @@
         <v>568004</v>
       </c>
     </row>
-    <row r="2104" spans="1:7">
+    <row r="2104" spans="1:5">
       <c r="A2104" t="s">
         <v>115</v>
       </c>
@@ -62955,7 +63105,7 @@
         <v>569036</v>
       </c>
     </row>
-    <row r="2142" spans="1:7">
+    <row r="2142" spans="1:5">
       <c r="A2142" t="s">
         <v>116</v>
       </c>
@@ -63015,7 +63165,7 @@
         <v>504001</v>
       </c>
     </row>
-    <row r="2145" spans="1:8">
+    <row r="2145" spans="1:7">
       <c r="A2145" t="s">
         <v>116</v>
       </c>
@@ -63035,7 +63185,7 @@
         <v>504002</v>
       </c>
     </row>
-    <row r="2146" spans="1:8">
+    <row r="2146" spans="1:7">
       <c r="A2146" t="s">
         <v>116</v>
       </c>
@@ -63055,7 +63205,7 @@
         <v>504003</v>
       </c>
     </row>
-    <row r="2147" spans="1:8">
+    <row r="2147" spans="1:7">
       <c r="A2147" t="s">
         <v>116</v>
       </c>
@@ -63075,7 +63225,7 @@
         <v>504004</v>
       </c>
     </row>
-    <row r="2148" spans="1:8">
+    <row r="2148" spans="1:5">
       <c r="A2148" t="s">
         <v>117</v>
       </c>
@@ -63092,7 +63242,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2149" spans="1:8">
+    <row r="2149" spans="1:7">
       <c r="A2149" t="s">
         <v>117</v>
       </c>
@@ -63112,7 +63262,7 @@
         <v>570001</v>
       </c>
     </row>
-    <row r="2150" spans="1:8">
+    <row r="2150" spans="1:7">
       <c r="A2150" t="s">
         <v>117</v>
       </c>
@@ -63250,7 +63400,7 @@
         <v>3354</v>
       </c>
     </row>
-    <row r="2156" spans="1:8">
+    <row r="2156" spans="1:5">
       <c r="A2156" t="s">
         <v>118</v>
       </c>
@@ -63267,7 +63417,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2157" spans="1:8">
+    <row r="2157" spans="1:7">
       <c r="A2157" t="s">
         <v>118</v>
       </c>
@@ -63287,7 +63437,7 @@
         <v>571001</v>
       </c>
     </row>
-    <row r="2158" spans="1:8">
+    <row r="2158" spans="1:7">
       <c r="A2158" t="s">
         <v>118</v>
       </c>
@@ -63307,7 +63457,7 @@
         <v>571002</v>
       </c>
     </row>
-    <row r="2159" spans="1:8">
+    <row r="2159" spans="1:7">
       <c r="A2159" t="s">
         <v>118</v>
       </c>
@@ -63327,7 +63477,7 @@
         <v>571003</v>
       </c>
     </row>
-    <row r="2160" spans="1:8">
+    <row r="2160" spans="1:7">
       <c r="A2160" t="s">
         <v>118</v>
       </c>
@@ -63393,7 +63543,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2163" spans="1:8">
+    <row r="2163" spans="1:7">
       <c r="A2163" t="s">
         <v>118</v>
       </c>
@@ -63413,7 +63563,7 @@
         <v>571007</v>
       </c>
     </row>
-    <row r="2164" spans="1:8">
+    <row r="2164" spans="1:7">
       <c r="A2164" t="s">
         <v>118</v>
       </c>
@@ -63433,7 +63583,7 @@
         <v>571008</v>
       </c>
     </row>
-    <row r="2165" spans="1:8">
+    <row r="2165" spans="1:7">
       <c r="A2165" t="s">
         <v>118</v>
       </c>
@@ -63453,7 +63603,7 @@
         <v>571009</v>
       </c>
     </row>
-    <row r="2166" spans="1:8">
+    <row r="2166" spans="1:7">
       <c r="A2166" t="s">
         <v>118</v>
       </c>
@@ -63473,7 +63623,7 @@
         <v>571010</v>
       </c>
     </row>
-    <row r="2167" spans="1:8">
+    <row r="2167" spans="1:5">
       <c r="A2167" t="s">
         <v>119</v>
       </c>
@@ -63490,7 +63640,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2168" spans="1:8">
+    <row r="2168" spans="1:7">
       <c r="A2168" t="s">
         <v>119</v>
       </c>
@@ -63510,7 +63660,7 @@
         <v>572001</v>
       </c>
     </row>
-    <row r="2169" spans="1:8">
+    <row r="2169" spans="1:7">
       <c r="A2169" t="s">
         <v>119</v>
       </c>
@@ -63599,7 +63749,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2173" spans="1:8">
+    <row r="2173" spans="1:7">
       <c r="A2173" t="s">
         <v>119</v>
       </c>
@@ -63619,7 +63769,7 @@
         <v>572006</v>
       </c>
     </row>
-    <row r="2174" spans="1:8">
+    <row r="2174" spans="1:7">
       <c r="A2174" t="s">
         <v>119</v>
       </c>
@@ -63639,7 +63789,7 @@
         <v>572007</v>
       </c>
     </row>
-    <row r="2175" spans="1:8">
+    <row r="2175" spans="1:7">
       <c r="A2175" t="s">
         <v>119</v>
       </c>
@@ -63659,7 +63809,7 @@
         <v>572008</v>
       </c>
     </row>
-    <row r="2176" spans="1:8">
+    <row r="2176" spans="1:7">
       <c r="A2176" t="s">
         <v>119</v>
       </c>
@@ -63679,7 +63829,7 @@
         <v>572009</v>
       </c>
     </row>
-    <row r="2177" spans="1:8">
+    <row r="2177" spans="1:7">
       <c r="A2177" t="s">
         <v>119</v>
       </c>
@@ -63699,7 +63849,7 @@
         <v>572010</v>
       </c>
     </row>
-    <row r="2178" spans="1:8">
+    <row r="2178" spans="1:5">
       <c r="A2178" t="s">
         <v>76</v>
       </c>
@@ -63716,7 +63866,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2179" spans="1:8">
+    <row r="2179" spans="1:7">
       <c r="A2179" t="s">
         <v>76</v>
       </c>
@@ -63739,7 +63889,7 @@
         <v>602000</v>
       </c>
     </row>
-    <row r="2180" spans="1:8">
+    <row r="2180" spans="1:7">
       <c r="A2180" t="s">
         <v>76</v>
       </c>
@@ -63759,7 +63909,7 @@
         <v>602001</v>
       </c>
     </row>
-    <row r="2181" spans="1:8">
+    <row r="2181" spans="1:7">
       <c r="A2181" t="s">
         <v>76</v>
       </c>
@@ -63779,7 +63929,7 @@
         <v>602002</v>
       </c>
     </row>
-    <row r="2182" spans="1:8">
+    <row r="2182" spans="1:7">
       <c r="A2182" t="s">
         <v>76</v>
       </c>
@@ -63845,7 +63995,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2185" spans="1:8">
+    <row r="2185" spans="1:7">
       <c r="A2185" t="s">
         <v>76</v>
       </c>
@@ -63888,7 +64038,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2187" spans="1:8">
+    <row r="2187" spans="1:7">
       <c r="A2187" t="s">
         <v>76</v>
       </c>
@@ -63908,7 +64058,7 @@
         <v>602008</v>
       </c>
     </row>
-    <row r="2188" spans="1:8">
+    <row r="2188" spans="1:7">
       <c r="A2188" t="s">
         <v>76</v>
       </c>
@@ -63928,7 +64078,7 @@
         <v>602009</v>
       </c>
     </row>
-    <row r="2189" spans="1:8">
+    <row r="2189" spans="1:7">
       <c r="A2189" t="s">
         <v>76</v>
       </c>
@@ -63948,7 +64098,7 @@
         <v>602010</v>
       </c>
     </row>
-    <row r="2190" spans="1:8">
+    <row r="2190" spans="1:7">
       <c r="A2190" t="s">
         <v>76</v>
       </c>
@@ -63968,7 +64118,7 @@
         <v>602011</v>
       </c>
     </row>
-    <row r="2191" spans="1:8">
+    <row r="2191" spans="1:7">
       <c r="A2191" t="s">
         <v>76</v>
       </c>
@@ -63988,7 +64138,7 @@
         <v>602012</v>
       </c>
     </row>
-    <row r="2192" spans="1:8">
+    <row r="2192" spans="1:7">
       <c r="A2192" t="s">
         <v>76</v>
       </c>
@@ -64008,7 +64158,7 @@
         <v>602013</v>
       </c>
     </row>
-    <row r="2193" spans="1:8">
+    <row r="2193" spans="1:7">
       <c r="A2193" t="s">
         <v>76</v>
       </c>
@@ -64028,7 +64178,7 @@
         <v>602014</v>
       </c>
     </row>
-    <row r="2194" spans="1:8">
+    <row r="2194" spans="1:7">
       <c r="A2194" t="s">
         <v>76</v>
       </c>
@@ -64048,7 +64198,7 @@
         <v>602015</v>
       </c>
     </row>
-    <row r="2195" spans="1:8">
+    <row r="2195" spans="1:5">
       <c r="A2195" t="s">
         <v>77</v>
       </c>
@@ -64065,7 +64215,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2196" spans="1:8">
+    <row r="2196" spans="1:7">
       <c r="A2196" t="s">
         <v>77</v>
       </c>
@@ -64088,7 +64238,7 @@
         <v>604000</v>
       </c>
     </row>
-    <row r="2197" spans="1:8">
+    <row r="2197" spans="1:7">
       <c r="A2197" t="s">
         <v>77</v>
       </c>
@@ -64108,7 +64258,7 @@
         <v>604001</v>
       </c>
     </row>
-    <row r="2198" spans="1:8">
+    <row r="2198" spans="1:7">
       <c r="A2198" t="s">
         <v>77</v>
       </c>
@@ -64128,7 +64278,7 @@
         <v>604002</v>
       </c>
     </row>
-    <row r="2199" spans="1:8">
+    <row r="2199" spans="1:7">
       <c r="A2199" t="s">
         <v>77</v>
       </c>
@@ -64217,7 +64367,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2203" spans="1:8">
+    <row r="2203" spans="1:7">
       <c r="A2203" t="s">
         <v>77</v>
       </c>
@@ -64329,7 +64479,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2208" spans="1:8">
+    <row r="2208" spans="1:7">
       <c r="A2208" t="s">
         <v>77</v>
       </c>
@@ -64349,7 +64499,7 @@
         <v>604012</v>
       </c>
     </row>
-    <row r="2209" spans="1:8">
+    <row r="2209" spans="1:7">
       <c r="A2209" t="s">
         <v>77</v>
       </c>
@@ -64369,7 +64519,7 @@
         <v>604013</v>
       </c>
     </row>
-    <row r="2210" spans="1:8">
+    <row r="2210" spans="1:7">
       <c r="A2210" t="s">
         <v>77</v>
       </c>
@@ -64389,7 +64539,7 @@
         <v>604014</v>
       </c>
     </row>
-    <row r="2211" spans="1:8">
+    <row r="2211" spans="1:7">
       <c r="A2211" t="s">
         <v>77</v>
       </c>
@@ -64409,7 +64559,7 @@
         <v>604015</v>
       </c>
     </row>
-    <row r="2212" spans="1:8">
+    <row r="2212" spans="1:7">
       <c r="A2212" t="s">
         <v>77</v>
       </c>
@@ -64429,7 +64579,7 @@
         <v>604016</v>
       </c>
     </row>
-    <row r="2213" spans="1:8">
+    <row r="2213" spans="1:7">
       <c r="A2213" t="s">
         <v>77</v>
       </c>
@@ -64449,7 +64599,7 @@
         <v>604017</v>
       </c>
     </row>
-    <row r="2214" spans="1:8">
+    <row r="2214" spans="1:7">
       <c r="A2214" t="s">
         <v>77</v>
       </c>
@@ -64469,7 +64619,7 @@
         <v>604018</v>
       </c>
     </row>
-    <row r="2215" spans="1:8">
+    <row r="2215" spans="1:5">
       <c r="A2215" t="s">
         <v>59</v>
       </c>
@@ -64512,7 +64662,7 @@
         <v>3691</v>
       </c>
     </row>
-    <row r="2217" spans="1:8">
+    <row r="2217" spans="1:7">
       <c r="A2217" t="s">
         <v>59</v>
       </c>
@@ -64532,7 +64682,7 @@
         <v>44001</v>
       </c>
     </row>
-    <row r="2218" spans="1:8">
+    <row r="2218" spans="1:7">
       <c r="A2218" t="s">
         <v>59</v>
       </c>
@@ -64667,7 +64817,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2224" spans="1:8">
+    <row r="2224" spans="1:7">
       <c r="A2224" t="s">
         <v>59</v>
       </c>
@@ -65078,7 +65228,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2242" spans="1:8">
+    <row r="2242" spans="1:7">
       <c r="A2242" t="s">
         <v>59</v>
       </c>
@@ -65098,7 +65248,7 @@
         <v>44185</v>
       </c>
     </row>
-    <row r="2243" spans="1:8">
+    <row r="2243" spans="1:7">
       <c r="A2243" t="s">
         <v>59</v>
       </c>
@@ -66843,7 +66993,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2319" spans="1:8">
+    <row r="2319" spans="1:7">
       <c r="A2319" t="s">
         <v>59</v>
       </c>
@@ -67231,7 +67381,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2336" spans="1:8">
+    <row r="2336" spans="1:7">
       <c r="A2336" t="s">
         <v>59</v>
       </c>
@@ -67251,7 +67401,7 @@
         <v>44188</v>
       </c>
     </row>
-    <row r="2337" spans="1:8">
+    <row r="2337" spans="1:7">
       <c r="A2337" t="s">
         <v>59</v>
       </c>
@@ -68651,7 +68801,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2398" spans="1:8">
+    <row r="2398" spans="1:5">
       <c r="A2398" t="s">
         <v>61</v>
       </c>
@@ -68691,7 +68841,7 @@
         <v>3691</v>
       </c>
     </row>
-    <row r="2400" spans="1:8">
+    <row r="2400" spans="1:7">
       <c r="A2400" t="s">
         <v>61</v>
       </c>
@@ -68711,7 +68861,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="2401" spans="1:8">
+    <row r="2401" spans="1:7">
       <c r="A2401" t="s">
         <v>61</v>
       </c>
@@ -68731,7 +68881,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="2402" spans="1:8">
+    <row r="2402" spans="1:7">
       <c r="A2402" t="s">
         <v>61</v>
       </c>
@@ -69165,7 +69315,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2421" spans="1:8">
+    <row r="2421" spans="1:7">
       <c r="A2421" t="s">
         <v>61</v>
       </c>
@@ -69185,7 +69335,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="2422" spans="1:8">
+    <row r="2422" spans="1:7">
       <c r="A2422" t="s">
         <v>61</v>
       </c>
@@ -69619,7 +69769,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2441" spans="1:8">
+    <row r="2441" spans="1:7">
       <c r="A2441" t="s">
         <v>61</v>
       </c>
@@ -69639,7 +69789,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="2442" spans="1:8">
+    <row r="2442" spans="1:7">
       <c r="A2442" t="s">
         <v>61</v>
       </c>
@@ -70855,7 +71005,7 @@
         <v>4051</v>
       </c>
     </row>
-    <row r="2495" spans="1:8">
+    <row r="2495" spans="1:5">
       <c r="A2495" t="s">
         <v>62</v>
       </c>
@@ -70872,7 +71022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2496" spans="1:8">
+    <row r="2496" spans="1:7">
       <c r="A2496" t="s">
         <v>62</v>
       </c>
@@ -70892,7 +71042,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="2497" spans="1:8">
+    <row r="2497" spans="1:7">
       <c r="A2497" t="s">
         <v>62</v>
       </c>
@@ -70912,7 +71062,7 @@
         <v>48001</v>
       </c>
     </row>
-    <row r="2498" spans="1:8">
+    <row r="2498" spans="1:7">
       <c r="A2498" t="s">
         <v>62</v>
       </c>
@@ -70932,7 +71082,7 @@
         <v>48163</v>
       </c>
     </row>
-    <row r="2499" spans="1:8">
+    <row r="2499" spans="1:7">
       <c r="A2499" t="s">
         <v>62</v>
       </c>
@@ -74609,7 +74759,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2659" spans="1:8">
+    <row r="2659" spans="1:7">
       <c r="A2659" t="s">
         <v>62</v>
       </c>
@@ -74629,7 +74779,7 @@
         <v>48101</v>
       </c>
     </row>
-    <row r="2660" spans="1:8">
+    <row r="2660" spans="1:5">
       <c r="A2660" t="s">
         <v>63</v>
       </c>
@@ -74646,7 +74796,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2661" spans="1:8">
+    <row r="2661" spans="1:7">
       <c r="A2661" t="s">
         <v>63</v>
       </c>
@@ -74666,7 +74816,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="2662" spans="1:8">
+    <row r="2662" spans="1:7">
       <c r="A2662" t="s">
         <v>63</v>
       </c>
@@ -75054,7 +75204,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2679" spans="1:8">
+    <row r="2679" spans="1:7">
       <c r="A2679" t="s">
         <v>63</v>
       </c>
@@ -75074,7 +75224,7 @@
         <v>42018</v>
       </c>
     </row>
-    <row r="2680" spans="1:8">
+    <row r="2680" spans="1:5">
       <c r="A2680" t="s">
         <v>120</v>
       </c>
@@ -75647,7 +75797,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H2679" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H2704" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -75656,6 +75806,209 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>4607</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4608</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>4610</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4611</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4612</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>4613</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4614</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>4616</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4617</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>4619</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4620</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>4622</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4623</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>4625</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4626</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>4628</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>4631</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4632</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>4634</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4635</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4638</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4639</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>4640</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>4641</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4642</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>4643</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>4644</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>4646</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>4647</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>4648</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>4649</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>4650</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>4651</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>4652</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>4653</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>4655</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>4656</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4657</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G24"/>
